--- a/src/BexioOrderImport.Tests/AnonymizedOrder.xlsx
+++ b/src/BexioOrderImport.Tests/AnonymizedOrder.xlsx
@@ -66,7 +66,7 @@
     <x:t>E-Mail:</x:t>
   </x:si>
   <x:si>
-    <x:t>test@test.com</x:t>
+    <x:t>chris@peakmile.com</x:t>
   </x:si>
   <x:si>
     <x:t>PLZ Ort:</x:t>
@@ -21018,7 +21018,7 @@
   </x:mergeCells>
   <x:phoneticPr fontId="20" type="noConversion"/>
   <x:hyperlinks>
-    <x:hyperlink ref="E5" r:id="rId11"/>
+    <x:hyperlink ref="E5" r:id="rId10"/>
   </x:hyperlinks>
   <x:printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.5905511811023623" bottom="0.5905511811023623" header="0.31496062992125984" footer="0.15748031496062992"/>

--- a/src/BexioOrderImport.Tests/AnonymizedOrder.xlsx
+++ b/src/BexioOrderImport.Tests/AnonymizedOrder.xlsx
@@ -21018,7 +21018,7 @@
   </x:mergeCells>
   <x:phoneticPr fontId="20" type="noConversion"/>
   <x:hyperlinks>
-    <x:hyperlink ref="E5" r:id="rId10"/>
+    <x:hyperlink ref="E5" r:id="rId11"/>
   </x:hyperlinks>
   <x:printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.5905511811023623" bottom="0.5905511811023623" header="0.31496062992125984" footer="0.15748031496062992"/>

--- a/src/BexioOrderImport.Tests/AnonymizedOrder.xlsx
+++ b/src/BexioOrderImport.Tests/AnonymizedOrder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projekte\bexio-order-import\src\BexioOrderImport.Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07DD237C-4E0F-42EA-ABA4-6428725A2BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AFB7328-5DE5-4251-A42D-C90644AA600C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <x:bookViews>
-    <x:workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="0" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <x:workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="0" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Ordersheeet" sheetId="9" r:id="rId1"/>
@@ -66,7 +66,7 @@
     <x:t>E-Mail:</x:t>
   </x:si>
   <x:si>
-    <x:t>chris@peakmile.com</x:t>
+    <x:t>test@test.com</x:t>
   </x:si>
   <x:si>
     <x:t>PLZ Ort:</x:t>
@@ -2929,31 +2929,31 @@
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1:AD466"/>
-  <x:sheetFormatPr defaultColWidth="12.139196" defaultRowHeight="13.8" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <x:sheetFormatPr defaultColWidth="12.139196" defaultRowHeight="12.75" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.886719" style="10" customWidth="1"/>
-    <x:col min="2" max="2" width="31.554688" style="55" customWidth="1" outlineLevel="1"/>
-    <x:col min="3" max="3" width="18.886719" style="12" customWidth="1" outlineLevel="1"/>
-    <x:col min="4" max="4" width="10.554688" style="12" customWidth="1" outlineLevel="1"/>
-    <x:col min="5" max="12" width="4.886719" style="8" customWidth="1" outlineLevel="1"/>
-    <x:col min="13" max="14" width="4.886719" style="8" customWidth="1"/>
-    <x:col min="15" max="18" width="4.886719" style="11" customWidth="1"/>
-    <x:col min="19" max="19" width="9.554688" style="10" customWidth="1"/>
-    <x:col min="20" max="20" width="7.554688" style="46" customWidth="1"/>
-    <x:col min="21" max="21" width="8.441406" style="40" customWidth="1"/>
-    <x:col min="22" max="22" width="14.886719" style="46" customWidth="1"/>
-    <x:col min="23" max="23" width="13.554688" style="46" customWidth="1"/>
-    <x:col min="24" max="24" width="12.109375" style="10" customWidth="1"/>
-    <x:col min="25" max="25" width="15.441406" style="40" customWidth="1"/>
-    <x:col min="26" max="26" width="14.441406" style="8" customWidth="1"/>
-    <x:col min="27" max="27" width="9.109375" style="8" customWidth="1"/>
+    <x:col min="1" max="1" width="9.855469" style="10" customWidth="1"/>
+    <x:col min="2" max="2" width="31.570312" style="55" customWidth="1" outlineLevel="1"/>
+    <x:col min="3" max="3" width="18.855469" style="12" customWidth="1" outlineLevel="1"/>
+    <x:col min="4" max="4" width="10.570312" style="12" customWidth="1" outlineLevel="1"/>
+    <x:col min="5" max="12" width="4.855469" style="8" customWidth="1" outlineLevel="1"/>
+    <x:col min="13" max="14" width="4.855469" style="8" customWidth="1"/>
+    <x:col min="15" max="18" width="4.855469" style="11" customWidth="1"/>
+    <x:col min="19" max="19" width="9.570312" style="10" customWidth="1"/>
+    <x:col min="20" max="20" width="7.570312" style="46" customWidth="1"/>
+    <x:col min="21" max="21" width="8.425781" style="40" customWidth="1"/>
+    <x:col min="22" max="22" width="14.855469" style="46" customWidth="1"/>
+    <x:col min="23" max="23" width="13.570312" style="46" customWidth="1"/>
+    <x:col min="24" max="24" width="12.140625" style="10" customWidth="1"/>
+    <x:col min="25" max="25" width="15.425781" style="40" customWidth="1"/>
+    <x:col min="26" max="26" width="14.425781" style="8" customWidth="1"/>
+    <x:col min="27" max="27" width="9.140625" style="8" customWidth="1"/>
     <x:col min="28" max="28" width="10" style="8" customWidth="1"/>
-    <x:col min="29" max="29" width="10.441406" style="8" customWidth="1"/>
-    <x:col min="30" max="30" width="10.109375" style="8" customWidth="1"/>
-    <x:col min="31" max="31" width="12.109375" style="0" customWidth="1"/>
+    <x:col min="29" max="29" width="10.425781" style="8" customWidth="1"/>
+    <x:col min="30" max="30" width="10.140625" style="8" customWidth="1"/>
+    <x:col min="31" max="31" width="12.140625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:31" ht="20.25" customHeight="1" s="15" customFormat="1" x14ac:dyDescent="0.4">
+    <x:row r="1" spans="1:31" ht="20.25" customHeight="1" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A1" s="54" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -2978,7 +2978,7 @@
       <x:c r="X1" s="43"/>
       <x:c r="Y1" s="37"/>
     </x:row>
-    <x:row r="2" spans="1:31" ht="20.25" customHeight="1" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <x:row r="2" spans="1:31" ht="20.25" customHeight="1" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <x:c r="A2" s="24"/>
       <x:c r="C2" s="14"/>
       <x:c r="D2" s="14"/>
@@ -3002,7 +3002,7 @@
       <x:c r="X2" s="24"/>
       <x:c r="Y2" s="38"/>
     </x:row>
-    <x:row r="3" spans="1:31" ht="19.35" customHeight="1" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <x:row r="3" spans="1:31" ht="19.35" customHeight="1" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <x:c r="A3" s="68" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -3026,7 +3026,7 @@
       <x:c r="X3" s="25"/>
       <x:c r="Y3" s="39"/>
     </x:row>
-    <x:row r="4" spans="1:31" ht="19.35" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="4" spans="1:31" ht="19.35" customHeight="1" x14ac:dyDescent="0.2">
       <x:c r="A4" s="62" t="s">
         <x:v>2</x:v>
       </x:c>
@@ -3045,7 +3045,7 @@
       <x:c r="Q4" s="8"/>
       <x:c r="R4" s="8"/>
     </x:row>
-    <x:row r="5" spans="1:31" ht="19.35" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="5" spans="1:31" ht="19.35" customHeight="1" x14ac:dyDescent="0.2">
       <x:c r="A5" s="62" t="s">
         <x:v>6</x:v>
       </x:c>
@@ -3064,7 +3064,7 @@
       <x:c r="Q5" s="8"/>
       <x:c r="R5" s="8"/>
     </x:row>
-    <x:row r="6" spans="1:31" ht="19.35" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="6" spans="1:31" ht="19.35" customHeight="1" x14ac:dyDescent="0.2">
       <x:c r="A6" s="62" t="s">
         <x:v>10</x:v>
       </x:c>
@@ -3083,7 +3083,7 @@
       <x:c r="V6" s="63"/>
       <x:c r="W6" s="63"/>
     </x:row>
-    <x:row r="7" spans="1:31" ht="19.35" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="7" spans="1:31" ht="19.35" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A7" s="62"/>
       <x:c r="B7" s="30"/>
       <x:c r="C7" s="8"/>
@@ -3106,7 +3106,7 @@
       <x:c r="V7" s="51"/>
       <x:c r="W7" s="62"/>
     </x:row>
-    <x:row r="8" spans="1:31" ht="15.6" customHeight="1" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <x:row r="8" spans="1:31" ht="15.6" customHeight="1" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <x:c r="A8" s="70" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -3135,7 +3135,7 @@
       <x:c r="X8" s="44"/>
       <x:c r="Y8" s="41"/>
     </x:row>
-    <x:row r="9" spans="1:31" ht="15" customHeight="1" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <x:row r="9" spans="1:31" ht="15" customHeight="1" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <x:c r="A9" s="71" t="s">
         <x:v>16</x:v>
       </x:c>
@@ -3164,7 +3164,7 @@
       <x:c r="X9" s="44"/>
       <x:c r="Y9" s="41"/>
     </x:row>
-    <x:row r="10" spans="1:31" ht="15.6" customHeight="1" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <x:row r="10" spans="1:31" ht="15.6" customHeight="1" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <x:c r="A10" s="69"/>
       <x:c r="B10" s="29"/>
       <x:c r="C10" s="23"/>
@@ -3214,7 +3214,7 @@
         <x:f>V11/100*V12</x:f>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:31" ht="16.35" customHeight="1" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <x:row r="11" spans="1:31" ht="16.35" customHeight="1" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <x:c r="A11" s="25"/>
       <x:c r="B11" s="34"/>
       <x:c r="C11" s="29"/>
@@ -3265,7 +3265,7 @@
         <x:f>V11-Z10</x:f>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:31" ht="16.5" customHeight="1" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <x:row r="12" spans="1:31" ht="16.5" customHeight="1" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <x:c r="A12" s="25"/>
       <x:c r="B12" s="34"/>
       <x:c r="C12" s="29"/>
@@ -3315,7 +3315,7 @@
       </x:c>
       <x:c r="W12" s="39"/>
     </x:row>
-    <x:row r="13" spans="1:31" ht="16.5" customHeight="1" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <x:row r="13" spans="1:31" ht="16.5" customHeight="1" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <x:c r="A13" s="25"/>
       <x:c r="B13" s="34"/>
       <x:c r="C13" s="29"/>
@@ -3364,7 +3364,7 @@
       </x:c>
       <x:c r="W13" s="39"/>
     </x:row>
-    <x:row r="14" spans="1:31" ht="18" customHeight="1" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <x:row r="14" spans="1:31" ht="18" customHeight="1" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <x:c r="A14" s="44"/>
       <x:c r="B14" s="55"/>
       <x:c r="C14" s="22"/>
@@ -3415,7 +3415,7 @@
       <x:c r="V14" s="44"/>
       <x:c r="W14" s="41"/>
     </x:row>
-    <x:row r="15" spans="1:31" ht="18" customHeight="1" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <x:row r="15" spans="1:31" ht="18" customHeight="1" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <x:c r="A15" s="44"/>
       <x:c r="B15" s="55"/>
       <x:c r="C15" s="66"/>
@@ -3468,7 +3468,7 @@
       </x:c>
       <x:c r="W15" s="41"/>
     </x:row>
-    <x:row r="16" spans="1:31" ht="18" customHeight="1" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <x:row r="16" spans="1:31" ht="18" customHeight="1" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <x:c r="A16" s="44"/>
       <x:c r="B16" s="55"/>
       <x:c r="C16" s="66"/>
@@ -3515,7 +3515,7 @@
       <x:c r="V16" s="44"/>
       <x:c r="W16" s="41"/>
     </x:row>
-    <x:row r="17" spans="1:31" ht="33" customHeight="1" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <x:row r="17" spans="1:31" ht="33" customHeight="1" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <x:c r="A17" s="139" t="s">
         <x:v>60</x:v>
       </x:c>
@@ -3586,7 +3586,7 @@
         <x:v>68</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="18" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A18" s="85">
         <x:v>5437</x:v>
       </x:c>
@@ -3626,7 +3626,7 @@
         <x:f>S18*T18</x:f>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="19" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A19" s="85">
         <x:v>5437</x:v>
       </x:c>
@@ -3666,7 +3666,7 @@
         <x:f>S19*T19</x:f>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="20" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A20" s="85">
         <x:v>5437</x:v>
       </x:c>
@@ -3706,7 +3706,7 @@
         <x:f>S20*T20</x:f>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="21" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A21" s="85">
         <x:v>5437</x:v>
       </x:c>
@@ -3746,7 +3746,7 @@
         <x:f>S21*T21</x:f>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="22" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A22" s="85">
         <x:v>5438</x:v>
       </x:c>
@@ -3786,7 +3786,7 @@
         <x:f>S22*T22</x:f>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="23" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A23" s="85">
         <x:v>5438</x:v>
       </x:c>
@@ -3826,7 +3826,7 @@
         <x:f>S23*T23</x:f>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="24" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A24" s="85">
         <x:v>5438</x:v>
       </x:c>
@@ -3866,7 +3866,7 @@
         <x:f>S24*T24</x:f>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="25" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A25" s="85">
         <x:v>5438</x:v>
       </x:c>
@@ -3906,7 +3906,7 @@
         <x:f>S25*T25</x:f>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="26" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A26" s="85">
         <x:v>5438</x:v>
       </x:c>
@@ -3946,7 +3946,7 @@
         <x:f>S26*T26</x:f>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="27" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A27" s="85">
         <x:v>5438</x:v>
       </x:c>
@@ -3986,7 +3986,7 @@
         <x:f>S27*T27</x:f>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="28" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A28" s="85">
         <x:v>5583</x:v>
       </x:c>
@@ -4026,7 +4026,7 @@
         <x:f>S28*T28</x:f>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="29" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A29" s="85">
         <x:v>5583</x:v>
       </x:c>
@@ -4066,7 +4066,7 @@
         <x:f>S29*T29</x:f>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="30" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A30" s="85">
         <x:v>5583</x:v>
       </x:c>
@@ -4106,7 +4106,7 @@
         <x:f>S30*T30</x:f>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="31" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A31" s="85">
         <x:v>5584</x:v>
       </x:c>
@@ -4146,7 +4146,7 @@
         <x:f>S31*T31</x:f>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="32" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A32" s="85">
         <x:v>5584</x:v>
       </x:c>
@@ -4186,7 +4186,7 @@
         <x:f>S32*T32</x:f>
       </x:c>
     </x:row>
-    <x:row r="33" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="33" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A33" s="85">
         <x:v>5586</x:v>
       </x:c>
@@ -4226,7 +4226,7 @@
         <x:f>S33*T33</x:f>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="34" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A34" s="85">
         <x:v>5586</x:v>
       </x:c>
@@ -4266,7 +4266,7 @@
         <x:f>S34*T34</x:f>
       </x:c>
     </x:row>
-    <x:row r="35" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="35" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A35" s="85">
         <x:v>5587</x:v>
       </x:c>
@@ -4306,7 +4306,7 @@
         <x:f>S35*T35</x:f>
       </x:c>
     </x:row>
-    <x:row r="36" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="36" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A36" s="85">
         <x:v>5587</x:v>
       </x:c>
@@ -4346,7 +4346,7 @@
         <x:f>S36*T36</x:f>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="37" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A37" s="85">
         <x:v>5587</x:v>
       </x:c>
@@ -4386,7 +4386,7 @@
         <x:f>S37*T37</x:f>
       </x:c>
     </x:row>
-    <x:row r="38" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="38" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A38" s="85">
         <x:v>5817</x:v>
       </x:c>
@@ -4426,7 +4426,7 @@
         <x:f>S38*T38</x:f>
       </x:c>
     </x:row>
-    <x:row r="39" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="39" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A39" s="85">
         <x:v>5817</x:v>
       </x:c>
@@ -4466,7 +4466,7 @@
         <x:f>S39*T39</x:f>
       </x:c>
     </x:row>
-    <x:row r="40" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="40" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A40" s="85">
         <x:v>5817</x:v>
       </x:c>
@@ -4506,7 +4506,7 @@
         <x:f>S40*T40</x:f>
       </x:c>
     </x:row>
-    <x:row r="41" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="41" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A41" s="85">
         <x:v>5817</x:v>
       </x:c>
@@ -4546,7 +4546,7 @@
         <x:f>S41*T41</x:f>
       </x:c>
     </x:row>
-    <x:row r="42" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="42" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A42" s="85">
         <x:v>5853</x:v>
       </x:c>
@@ -4586,7 +4586,7 @@
         <x:f>S42*T42</x:f>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="43" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A43" s="85">
         <x:v>5968</x:v>
       </x:c>
@@ -4626,7 +4626,7 @@
         <x:f>S43*T43</x:f>
       </x:c>
     </x:row>
-    <x:row r="44" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="44" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A44" s="85">
         <x:v>5968</x:v>
       </x:c>
@@ -4666,7 +4666,7 @@
         <x:f>S44*T44</x:f>
       </x:c>
     </x:row>
-    <x:row r="45" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="45" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A45" s="85">
         <x:v>5968</x:v>
       </x:c>
@@ -4706,7 +4706,7 @@
         <x:f>S45*T45</x:f>
       </x:c>
     </x:row>
-    <x:row r="46" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="46" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A46" s="85">
         <x:v>5968</x:v>
       </x:c>
@@ -4746,7 +4746,7 @@
         <x:f>S46*T46</x:f>
       </x:c>
     </x:row>
-    <x:row r="47" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="47" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A47" s="85">
         <x:v>5968</x:v>
       </x:c>
@@ -4786,7 +4786,7 @@
         <x:f>S47*T47</x:f>
       </x:c>
     </x:row>
-    <x:row r="48" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="48" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A48" s="85">
         <x:v>5969</x:v>
       </x:c>
@@ -4826,7 +4826,7 @@
         <x:f>S48*T48</x:f>
       </x:c>
     </x:row>
-    <x:row r="49" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="49" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A49" s="85">
         <x:v>5969</x:v>
       </x:c>
@@ -4866,7 +4866,7 @@
         <x:f>S49*T49</x:f>
       </x:c>
     </x:row>
-    <x:row r="50" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="50" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A50" s="85">
         <x:v>5969</x:v>
       </x:c>
@@ -4906,7 +4906,7 @@
         <x:f>S50*T50</x:f>
       </x:c>
     </x:row>
-    <x:row r="51" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="51" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A51" s="85">
         <x:v>5970</x:v>
       </x:c>
@@ -4946,7 +4946,7 @@
         <x:f>S51*T51</x:f>
       </x:c>
     </x:row>
-    <x:row r="52" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="52" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A52" s="85">
         <x:v>5970</x:v>
       </x:c>
@@ -4986,7 +4986,7 @@
         <x:f>S52*T52</x:f>
       </x:c>
     </x:row>
-    <x:row r="53" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="53" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A53" s="85">
         <x:v>5970</x:v>
       </x:c>
@@ -5026,7 +5026,7 @@
         <x:f>S53*T53</x:f>
       </x:c>
     </x:row>
-    <x:row r="54" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="54" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A54" s="85">
         <x:v>5970</x:v>
       </x:c>
@@ -5066,7 +5066,7 @@
         <x:f>S54*T54</x:f>
       </x:c>
     </x:row>
-    <x:row r="55" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="55" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A55" s="85">
         <x:v>5971</x:v>
       </x:c>
@@ -5106,7 +5106,7 @@
         <x:f>S55*T55</x:f>
       </x:c>
     </x:row>
-    <x:row r="56" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="56" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A56" s="85">
         <x:v>6118</x:v>
       </x:c>
@@ -5146,7 +5146,7 @@
         <x:f>S56*T56</x:f>
       </x:c>
     </x:row>
-    <x:row r="57" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="57" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A57" s="85">
         <x:v>6118</x:v>
       </x:c>
@@ -5186,7 +5186,7 @@
         <x:f>S57*T57</x:f>
       </x:c>
     </x:row>
-    <x:row r="58" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="58" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A58" s="85">
         <x:v>6119</x:v>
       </x:c>
@@ -5226,7 +5226,7 @@
         <x:f>S58*T58</x:f>
       </x:c>
     </x:row>
-    <x:row r="59" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="59" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A59" s="85">
         <x:v>6120</x:v>
       </x:c>
@@ -5266,7 +5266,7 @@
         <x:f>S59*T59</x:f>
       </x:c>
     </x:row>
-    <x:row r="60" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="60" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A60" s="85">
         <x:v>6141</x:v>
       </x:c>
@@ -5306,7 +5306,7 @@
         <x:f>S60*T60</x:f>
       </x:c>
     </x:row>
-    <x:row r="61" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="61" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A61" s="85">
         <x:v>6141</x:v>
       </x:c>
@@ -5346,7 +5346,7 @@
         <x:f>S61*T61</x:f>
       </x:c>
     </x:row>
-    <x:row r="62" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="62" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A62" s="85">
         <x:v>6141</x:v>
       </x:c>
@@ -5386,7 +5386,7 @@
         <x:f>S62*T62</x:f>
       </x:c>
     </x:row>
-    <x:row r="63" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="63" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A63" s="85">
         <x:v>6145</x:v>
       </x:c>
@@ -5426,7 +5426,7 @@
         <x:f>S63*T63</x:f>
       </x:c>
     </x:row>
-    <x:row r="64" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="64" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A64" s="85">
         <x:v>6145</x:v>
       </x:c>
@@ -5466,7 +5466,7 @@
         <x:f>S64*T64</x:f>
       </x:c>
     </x:row>
-    <x:row r="65" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="65" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A65" s="85">
         <x:v>6147</x:v>
       </x:c>
@@ -5506,7 +5506,7 @@
         <x:f>S65*T65</x:f>
       </x:c>
     </x:row>
-    <x:row r="66" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="66" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A66" s="85">
         <x:v>6343</x:v>
       </x:c>
@@ -5546,7 +5546,7 @@
         <x:f>S66*T66</x:f>
       </x:c>
     </x:row>
-    <x:row r="67" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="67" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A67" s="85">
         <x:v>6344</x:v>
       </x:c>
@@ -5586,7 +5586,7 @@
         <x:f>S67*T67</x:f>
       </x:c>
     </x:row>
-    <x:row r="68" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="68" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A68" s="85">
         <x:v>6520</x:v>
       </x:c>
@@ -5626,7 +5626,7 @@
         <x:f>S68*T68</x:f>
       </x:c>
     </x:row>
-    <x:row r="69" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="69" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A69" s="85">
         <x:v>6534</x:v>
       </x:c>
@@ -5666,7 +5666,7 @@
         <x:f>S69*T69</x:f>
       </x:c>
     </x:row>
-    <x:row r="70" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="70" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A70" s="85">
         <x:v>6534</x:v>
       </x:c>
@@ -5706,7 +5706,7 @@
         <x:f>S70*T70</x:f>
       </x:c>
     </x:row>
-    <x:row r="71" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="71" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A71" s="85">
         <x:v>6722</x:v>
       </x:c>
@@ -5746,7 +5746,7 @@
         <x:f>S71*T71</x:f>
       </x:c>
     </x:row>
-    <x:row r="72" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="72" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A72" s="85">
         <x:v>6722</x:v>
       </x:c>
@@ -5786,7 +5786,7 @@
         <x:f>S72*T72</x:f>
       </x:c>
     </x:row>
-    <x:row r="73" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="73" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A73" s="87">
         <x:v>6846</x:v>
       </x:c>
@@ -5826,7 +5826,7 @@
         <x:f>S73*T73</x:f>
       </x:c>
     </x:row>
-    <x:row r="74" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="74" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A74" s="87">
         <x:v>6846</x:v>
       </x:c>
@@ -5866,7 +5866,7 @@
         <x:f>S74*T74</x:f>
       </x:c>
     </x:row>
-    <x:row r="75" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="75" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A75" s="85">
         <x:v>6847</x:v>
       </x:c>
@@ -5906,7 +5906,7 @@
         <x:f>S75*T75</x:f>
       </x:c>
     </x:row>
-    <x:row r="76" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="76" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A76" s="85">
         <x:v>6847</x:v>
       </x:c>
@@ -5946,7 +5946,7 @@
         <x:f>S76*T76</x:f>
       </x:c>
     </x:row>
-    <x:row r="77" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="77" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A77" s="85">
         <x:v>6847</x:v>
       </x:c>
@@ -5986,7 +5986,7 @@
         <x:f>S77*T77</x:f>
       </x:c>
     </x:row>
-    <x:row r="78" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="78" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A78" s="85">
         <x:v>6847</x:v>
       </x:c>
@@ -6026,7 +6026,7 @@
         <x:f>S78*T78</x:f>
       </x:c>
     </x:row>
-    <x:row r="79" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="79" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A79" s="85">
         <x:v>6847</x:v>
       </x:c>
@@ -6066,7 +6066,7 @@
         <x:f>S79*T79</x:f>
       </x:c>
     </x:row>
-    <x:row r="80" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="80" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A80" s="85">
         <x:v>6847</x:v>
       </x:c>
@@ -6106,7 +6106,7 @@
         <x:f>S80*T80</x:f>
       </x:c>
     </x:row>
-    <x:row r="81" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="81" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A81" s="85">
         <x:v>6848</x:v>
       </x:c>
@@ -6146,7 +6146,7 @@
         <x:f>S81*T81</x:f>
       </x:c>
     </x:row>
-    <x:row r="82" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="82" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A82" s="85">
         <x:v>6848</x:v>
       </x:c>
@@ -6186,7 +6186,7 @@
         <x:f>S82*T82</x:f>
       </x:c>
     </x:row>
-    <x:row r="83" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="83" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A83" s="85">
         <x:v>6848</x:v>
       </x:c>
@@ -6226,7 +6226,7 @@
         <x:f>S83*T83</x:f>
       </x:c>
     </x:row>
-    <x:row r="84" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="84" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A84" s="85">
         <x:v>6848</x:v>
       </x:c>
@@ -6266,7 +6266,7 @@
         <x:f>S84*T84</x:f>
       </x:c>
     </x:row>
-    <x:row r="85" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="85" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A85" s="85">
         <x:v>6848</x:v>
       </x:c>
@@ -6306,7 +6306,7 @@
         <x:f>S85*T85</x:f>
       </x:c>
     </x:row>
-    <x:row r="86" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="86" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A86" s="85">
         <x:v>6848</x:v>
       </x:c>
@@ -6346,7 +6346,7 @@
         <x:f>S86*T86</x:f>
       </x:c>
     </x:row>
-    <x:row r="87" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="87" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A87" s="85">
         <x:v>6849</x:v>
       </x:c>
@@ -6386,7 +6386,7 @@
         <x:f>S87*T87</x:f>
       </x:c>
     </x:row>
-    <x:row r="88" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="88" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A88" s="85">
         <x:v>6850</x:v>
       </x:c>
@@ -6426,7 +6426,7 @@
         <x:f>S88*T88</x:f>
       </x:c>
     </x:row>
-    <x:row r="89" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="89" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A89" s="85">
         <x:v>6850</x:v>
       </x:c>
@@ -6466,7 +6466,7 @@
         <x:f>S89*T89</x:f>
       </x:c>
     </x:row>
-    <x:row r="90" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="90" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A90" s="85">
         <x:v>6850</x:v>
       </x:c>
@@ -6506,7 +6506,7 @@
         <x:f>S90*T90</x:f>
       </x:c>
     </x:row>
-    <x:row r="91" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="91" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A91" s="85">
         <x:v>6850</x:v>
       </x:c>
@@ -6546,7 +6546,7 @@
         <x:f>S91*T91</x:f>
       </x:c>
     </x:row>
-    <x:row r="92" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="92" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A92" s="85">
         <x:v>6850</x:v>
       </x:c>
@@ -6586,7 +6586,7 @@
         <x:f>S92*T92</x:f>
       </x:c>
     </x:row>
-    <x:row r="93" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="93" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A93" s="85">
         <x:v>6850</x:v>
       </x:c>
@@ -6626,7 +6626,7 @@
         <x:f>S93*T93</x:f>
       </x:c>
     </x:row>
-    <x:row r="94" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="94" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A94" s="85">
         <x:v>6851</x:v>
       </x:c>
@@ -6666,7 +6666,7 @@
         <x:f>S94*T94</x:f>
       </x:c>
     </x:row>
-    <x:row r="95" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="95" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A95" s="85">
         <x:v>6851</x:v>
       </x:c>
@@ -6706,7 +6706,7 @@
         <x:f>S95*T95</x:f>
       </x:c>
     </x:row>
-    <x:row r="96" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="96" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A96" s="85">
         <x:v>6851</x:v>
       </x:c>
@@ -6746,7 +6746,7 @@
         <x:f>S96*T96</x:f>
       </x:c>
     </x:row>
-    <x:row r="97" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="97" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A97" s="85">
         <x:v>6851</x:v>
       </x:c>
@@ -6786,7 +6786,7 @@
         <x:f>S97*T97</x:f>
       </x:c>
     </x:row>
-    <x:row r="98" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="98" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A98" s="85">
         <x:v>6851</x:v>
       </x:c>
@@ -6826,7 +6826,7 @@
         <x:f>S98*T98</x:f>
       </x:c>
     </x:row>
-    <x:row r="99" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="99" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A99" s="85">
         <x:v>6851</x:v>
       </x:c>
@@ -6866,7 +6866,7 @@
         <x:f>S99*T99</x:f>
       </x:c>
     </x:row>
-    <x:row r="100" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="100" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A100" s="85">
         <x:v>6851</x:v>
       </x:c>
@@ -6906,7 +6906,7 @@
         <x:f>S100*T100</x:f>
       </x:c>
     </x:row>
-    <x:row r="101" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="101" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A101" s="85">
         <x:v>6851</x:v>
       </x:c>
@@ -6946,7 +6946,7 @@
         <x:f>S101*T101</x:f>
       </x:c>
     </x:row>
-    <x:row r="102" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="102" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A102" s="85">
         <x:v>6851</x:v>
       </x:c>
@@ -6986,7 +6986,7 @@
         <x:f>S102*T102</x:f>
       </x:c>
     </x:row>
-    <x:row r="103" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="103" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A103" s="85">
         <x:v>6851</x:v>
       </x:c>
@@ -7026,7 +7026,7 @@
         <x:f>S103*T103</x:f>
       </x:c>
     </x:row>
-    <x:row r="104" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="104" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A104" s="87">
         <x:v>6852</x:v>
       </x:c>
@@ -7066,7 +7066,7 @@
         <x:f>S104*T104</x:f>
       </x:c>
     </x:row>
-    <x:row r="105" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="105" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A105" s="87">
         <x:v>6852</x:v>
       </x:c>
@@ -7106,7 +7106,7 @@
         <x:f>S105*T105</x:f>
       </x:c>
     </x:row>
-    <x:row r="106" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="106" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A106" s="87">
         <x:v>6852</x:v>
       </x:c>
@@ -7146,7 +7146,7 @@
         <x:f>S106*T106</x:f>
       </x:c>
     </x:row>
-    <x:row r="107" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="107" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A107" s="87">
         <x:v>6852</x:v>
       </x:c>
@@ -7186,7 +7186,7 @@
         <x:f>S107*T107</x:f>
       </x:c>
     </x:row>
-    <x:row r="108" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="108" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A108" s="87">
         <x:v>6852</x:v>
       </x:c>
@@ -7226,7 +7226,7 @@
         <x:f>S108*T108</x:f>
       </x:c>
     </x:row>
-    <x:row r="109" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="109" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A109" s="87">
         <x:v>6852</x:v>
       </x:c>
@@ -7266,7 +7266,7 @@
         <x:f>S109*T109</x:f>
       </x:c>
     </x:row>
-    <x:row r="110" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="110" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A110" s="85">
         <x:v>6925</x:v>
       </x:c>
@@ -7308,7 +7308,7 @@
       <x:c r="X110" s="55"/>
       <x:c r="Y110" s="93"/>
     </x:row>
-    <x:row r="111" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="111" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.2">
       <x:c r="A111" s="85">
         <x:v>6925</x:v>
       </x:c>
@@ -7350,7 +7350,7 @@
       <x:c r="X111" s="55"/>
       <x:c r="Y111" s="93"/>
     </x:row>
-    <x:row r="112" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="112" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A112" s="87">
         <x:v>720410</x:v>
       </x:c>
@@ -7392,7 +7392,7 @@
       <x:c r="X112" s="55"/>
       <x:c r="Y112" s="93"/>
     </x:row>
-    <x:row r="113" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="113" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A113" s="87">
         <x:v>720410</x:v>
       </x:c>
@@ -7434,7 +7434,7 @@
       <x:c r="X113" s="55"/>
       <x:c r="Y113" s="93"/>
     </x:row>
-    <x:row r="114" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="114" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A114" s="87">
         <x:v>720410</x:v>
       </x:c>
@@ -7474,7 +7474,7 @@
         <x:f>S114*T114</x:f>
       </x:c>
     </x:row>
-    <x:row r="115" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="115" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A115" s="87">
         <x:v>720410</x:v>
       </x:c>
@@ -7514,7 +7514,7 @@
         <x:f>S115*T115</x:f>
       </x:c>
     </x:row>
-    <x:row r="116" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="116" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A116" s="87">
         <x:v>720410</x:v>
       </x:c>
@@ -7554,7 +7554,7 @@
         <x:f>S116*T116</x:f>
       </x:c>
     </x:row>
-    <x:row r="117" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="117" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A117" s="87">
         <x:v>720410</x:v>
       </x:c>
@@ -7594,7 +7594,7 @@
         <x:f>S117*T117</x:f>
       </x:c>
     </x:row>
-    <x:row r="118" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="118" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A118" s="87">
         <x:v>720412</x:v>
       </x:c>
@@ -7634,7 +7634,7 @@
         <x:f>S118*T118</x:f>
       </x:c>
     </x:row>
-    <x:row r="119" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="119" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A119" s="87">
         <x:v>720412</x:v>
       </x:c>
@@ -7674,7 +7674,7 @@
         <x:f>S119*T119</x:f>
       </x:c>
     </x:row>
-    <x:row r="120" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="120" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A120" s="87">
         <x:v>720414</x:v>
       </x:c>
@@ -7714,7 +7714,7 @@
         <x:f>S120*T120</x:f>
       </x:c>
     </x:row>
-    <x:row r="121" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="121" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A121" s="87">
         <x:v>720414</x:v>
       </x:c>
@@ -7754,7 +7754,7 @@
         <x:f>S121*T121</x:f>
       </x:c>
     </x:row>
-    <x:row r="122" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="122" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A122" s="87">
         <x:v>720414</x:v>
       </x:c>
@@ -7794,7 +7794,7 @@
         <x:f>S122*T122</x:f>
       </x:c>
     </x:row>
-    <x:row r="123" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="123" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A123" s="87">
         <x:v>720414</x:v>
       </x:c>
@@ -7834,7 +7834,7 @@
         <x:f>S123*T123</x:f>
       </x:c>
     </x:row>
-    <x:row r="124" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="124" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A124" s="87">
         <x:v>1234</x:v>
       </x:c>
@@ -7882,7 +7882,7 @@
         <x:f>S124*T124</x:f>
       </x:c>
     </x:row>
-    <x:row r="125" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="125" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A125" s="87">
         <x:v>720419</x:v>
       </x:c>
@@ -7922,7 +7922,7 @@
         <x:f>S125*T125</x:f>
       </x:c>
     </x:row>
-    <x:row r="126" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="126" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A126" s="87">
         <x:v>720419</x:v>
       </x:c>
@@ -7962,7 +7962,7 @@
         <x:f>S126*T126</x:f>
       </x:c>
     </x:row>
-    <x:row r="127" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="127" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A127" s="87">
         <x:v>720419</x:v>
       </x:c>
@@ -8002,7 +8002,7 @@
         <x:f>S127*T127</x:f>
       </x:c>
     </x:row>
-    <x:row r="128" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="128" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A128" s="87">
         <x:v>720419</x:v>
       </x:c>
@@ -8042,7 +8042,7 @@
         <x:f>S128*T128</x:f>
       </x:c>
     </x:row>
-    <x:row r="129" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="129" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A129" s="87">
         <x:v>720421</x:v>
       </x:c>
@@ -8082,7 +8082,7 @@
         <x:f>S129*T129</x:f>
       </x:c>
     </x:row>
-    <x:row r="130" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="130" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A130" s="87">
         <x:v>720421</x:v>
       </x:c>
@@ -8122,7 +8122,7 @@
         <x:f>S130*T130</x:f>
       </x:c>
     </x:row>
-    <x:row r="131" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="131" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A131" s="87">
         <x:v>720421</x:v>
       </x:c>
@@ -8162,7 +8162,7 @@
         <x:f>S131*T131</x:f>
       </x:c>
     </x:row>
-    <x:row r="132" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="132" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A132" s="87">
         <x:v>720421</x:v>
       </x:c>
@@ -8202,7 +8202,7 @@
         <x:f>S132*T132</x:f>
       </x:c>
     </x:row>
-    <x:row r="133" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="133" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A133" s="87">
         <x:v>720423</x:v>
       </x:c>
@@ -8242,7 +8242,7 @@
         <x:f>S133*T133</x:f>
       </x:c>
     </x:row>
-    <x:row r="134" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="134" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A134" s="87">
         <x:v>720423</x:v>
       </x:c>
@@ -8282,7 +8282,7 @@
         <x:f>S134*T134</x:f>
       </x:c>
     </x:row>
-    <x:row r="135" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="135" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A135" s="87"/>
       <x:c r="B135" s="87"/>
       <x:c r="C135" s="87"/>
@@ -8306,7 +8306,7 @@
       <x:c r="U135" s="88"/>
       <x:c r="V135" s="108"/>
     </x:row>
-    <x:row r="136" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="136" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A136" s="87"/>
       <x:c r="B136" s="87"/>
       <x:c r="C136" s="87"/>
@@ -8330,7 +8330,7 @@
       <x:c r="U136" s="88"/>
       <x:c r="V136" s="108"/>
     </x:row>
-    <x:row r="137" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="137" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A137" s="87"/>
       <x:c r="B137" s="87"/>
       <x:c r="C137" s="87"/>
@@ -8354,7 +8354,7 @@
       <x:c r="U137" s="88"/>
       <x:c r="V137" s="108"/>
     </x:row>
-    <x:row r="138" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="138" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A138" s="87"/>
       <x:c r="B138" s="87"/>
       <x:c r="C138" s="87"/>
@@ -8378,7 +8378,7 @@
       <x:c r="U138" s="88"/>
       <x:c r="V138" s="108"/>
     </x:row>
-    <x:row r="139" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="139" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A139" s="87">
         <x:v>720432</x:v>
       </x:c>
@@ -8418,7 +8418,7 @@
         <x:f>S139*T139</x:f>
       </x:c>
     </x:row>
-    <x:row r="140" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="140" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A140" s="87">
         <x:v>720433</x:v>
       </x:c>
@@ -8458,7 +8458,7 @@
         <x:f>S140*T140</x:f>
       </x:c>
     </x:row>
-    <x:row r="141" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="141" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A141" s="87"/>
       <x:c r="B141" s="87"/>
       <x:c r="C141" s="87"/>
@@ -8482,7 +8482,7 @@
       <x:c r="U141" s="88"/>
       <x:c r="V141" s="108"/>
     </x:row>
-    <x:row r="142" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="142" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A142" s="87">
         <x:v>720435</x:v>
       </x:c>
@@ -8522,7 +8522,7 @@
         <x:f>S142*T142</x:f>
       </x:c>
     </x:row>
-    <x:row r="143" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="143" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A143" s="87">
         <x:v>720435</x:v>
       </x:c>
@@ -8562,7 +8562,7 @@
         <x:f>S143*T143</x:f>
       </x:c>
     </x:row>
-    <x:row r="144" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="144" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A144" s="87">
         <x:v>720435</x:v>
       </x:c>
@@ -8602,7 +8602,7 @@
         <x:f>S144*T144</x:f>
       </x:c>
     </x:row>
-    <x:row r="145" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="145" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A145" s="87">
         <x:v>720437</x:v>
       </x:c>
@@ -8642,7 +8642,7 @@
         <x:f>S145*T145</x:f>
       </x:c>
     </x:row>
-    <x:row r="146" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="146" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A146" s="87">
         <x:v>720437</x:v>
       </x:c>
@@ -8682,7 +8682,7 @@
         <x:f>S146*T146</x:f>
       </x:c>
     </x:row>
-    <x:row r="147" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="147" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A147" s="87">
         <x:v>720450</x:v>
       </x:c>
@@ -8722,7 +8722,7 @@
         <x:f>S147*T147</x:f>
       </x:c>
     </x:row>
-    <x:row r="148" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="148" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A148" s="87">
         <x:v>720450</x:v>
       </x:c>
@@ -8762,7 +8762,7 @@
         <x:f>S148*T148</x:f>
       </x:c>
     </x:row>
-    <x:row r="149" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="149" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A149" s="87">
         <x:v>720450</x:v>
       </x:c>
@@ -8802,7 +8802,7 @@
         <x:f>S149*T149</x:f>
       </x:c>
     </x:row>
-    <x:row r="150" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="150" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A150" s="87">
         <x:v>720451</x:v>
       </x:c>
@@ -8842,7 +8842,7 @@
         <x:f>S150*T150</x:f>
       </x:c>
     </x:row>
-    <x:row r="151" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="151" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A151" s="87">
         <x:v>720451</x:v>
       </x:c>
@@ -8882,7 +8882,7 @@
         <x:f>S151*T151</x:f>
       </x:c>
     </x:row>
-    <x:row r="152" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="152" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A152" s="87">
         <x:v>720453</x:v>
       </x:c>
@@ -8922,7 +8922,7 @@
         <x:f>S152*T152</x:f>
       </x:c>
     </x:row>
-    <x:row r="153" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="153" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A153" s="87">
         <x:v>720453</x:v>
       </x:c>
@@ -8962,7 +8962,7 @@
         <x:f>S153*T153</x:f>
       </x:c>
     </x:row>
-    <x:row r="154" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="154" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A154" s="87">
         <x:v>720453</x:v>
       </x:c>
@@ -9002,7 +9002,7 @@
         <x:f>S154*T154</x:f>
       </x:c>
     </x:row>
-    <x:row r="155" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="155" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A155" s="87">
         <x:v>720454</x:v>
       </x:c>
@@ -9042,7 +9042,7 @@
         <x:f>S155*T155</x:f>
       </x:c>
     </x:row>
-    <x:row r="156" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="156" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A156" s="87">
         <x:v>720454</x:v>
       </x:c>
@@ -9082,7 +9082,7 @@
         <x:f>S156*T156</x:f>
       </x:c>
     </x:row>
-    <x:row r="157" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="157" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A157" s="87">
         <x:v>720454</x:v>
       </x:c>
@@ -9122,7 +9122,7 @@
         <x:f>S157*T157</x:f>
       </x:c>
     </x:row>
-    <x:row r="158" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="158" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A158" s="87">
         <x:v>720455</x:v>
       </x:c>
@@ -9162,7 +9162,7 @@
         <x:f>S158*T158</x:f>
       </x:c>
     </x:row>
-    <x:row r="159" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="159" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A159" s="87">
         <x:v>720455</x:v>
       </x:c>
@@ -9202,7 +9202,7 @@
         <x:f>S159*T159</x:f>
       </x:c>
     </x:row>
-    <x:row r="160" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="160" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A160" s="87">
         <x:v>720456</x:v>
       </x:c>
@@ -9242,7 +9242,7 @@
         <x:f>S160*T160</x:f>
       </x:c>
     </x:row>
-    <x:row r="161" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="161" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A161" s="87">
         <x:v>720456</x:v>
       </x:c>
@@ -9282,7 +9282,7 @@
         <x:f>S161*T161</x:f>
       </x:c>
     </x:row>
-    <x:row r="162" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="162" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A162" s="87">
         <x:v>720460</x:v>
       </x:c>
@@ -9322,7 +9322,7 @@
         <x:f>S162*T162</x:f>
       </x:c>
     </x:row>
-    <x:row r="163" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="163" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A163" s="87">
         <x:v>720460</x:v>
       </x:c>
@@ -9362,7 +9362,7 @@
         <x:f>S163*T163</x:f>
       </x:c>
     </x:row>
-    <x:row r="164" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="164" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A164" s="87">
         <x:v>720464</x:v>
       </x:c>
@@ -9402,7 +9402,7 @@
         <x:f>S164*T164</x:f>
       </x:c>
     </x:row>
-    <x:row r="165" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="165" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A165" s="87">
         <x:v>720465</x:v>
       </x:c>
@@ -9442,7 +9442,7 @@
         <x:f>S165*T165</x:f>
       </x:c>
     </x:row>
-    <x:row r="166" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="166" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A166" s="87">
         <x:v>720470</x:v>
       </x:c>
@@ -9482,7 +9482,7 @@
         <x:f>S166*T166</x:f>
       </x:c>
     </x:row>
-    <x:row r="167" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="167" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A167" s="87">
         <x:v>720470</x:v>
       </x:c>
@@ -9522,7 +9522,7 @@
         <x:f>S167*T167</x:f>
       </x:c>
     </x:row>
-    <x:row r="168" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="168" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A168" s="87">
         <x:v>720470</x:v>
       </x:c>
@@ -9562,7 +9562,7 @@
         <x:f>S168*T168</x:f>
       </x:c>
     </x:row>
-    <x:row r="169" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="169" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A169" s="87">
         <x:v>720471</x:v>
       </x:c>
@@ -9602,7 +9602,7 @@
         <x:f>S169*T169</x:f>
       </x:c>
     </x:row>
-    <x:row r="170" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="170" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A170" s="87">
         <x:v>720471</x:v>
       </x:c>
@@ -9642,7 +9642,7 @@
         <x:f>S170*T170</x:f>
       </x:c>
     </x:row>
-    <x:row r="171" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="171" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A171" s="87">
         <x:v>720471</x:v>
       </x:c>
@@ -9682,7 +9682,7 @@
         <x:f>S171*T171</x:f>
       </x:c>
     </x:row>
-    <x:row r="172" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="172" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A172" s="87">
         <x:v>720472</x:v>
       </x:c>
@@ -9722,7 +9722,7 @@
         <x:f>S172*T172</x:f>
       </x:c>
     </x:row>
-    <x:row r="173" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="173" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A173" s="87">
         <x:v>720472</x:v>
       </x:c>
@@ -9762,7 +9762,7 @@
         <x:f>S173*T173</x:f>
       </x:c>
     </x:row>
-    <x:row r="174" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="174" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A174" s="87">
         <x:v>720473</x:v>
       </x:c>
@@ -9802,7 +9802,7 @@
         <x:f>S174*T174</x:f>
       </x:c>
     </x:row>
-    <x:row r="175" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="175" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A175" s="87">
         <x:v>720473</x:v>
       </x:c>
@@ -9842,7 +9842,7 @@
         <x:f>S175*T175</x:f>
       </x:c>
     </x:row>
-    <x:row r="176" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="176" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A176" s="87">
         <x:v>720481</x:v>
       </x:c>
@@ -9882,7 +9882,7 @@
         <x:f>S176*T176</x:f>
       </x:c>
     </x:row>
-    <x:row r="177" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="177" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A177" s="87">
         <x:v>720481</x:v>
       </x:c>
@@ -9922,7 +9922,7 @@
         <x:f>S177*T177</x:f>
       </x:c>
     </x:row>
-    <x:row r="178" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="178" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A178" s="87">
         <x:v>720482</x:v>
       </x:c>
@@ -9962,7 +9962,7 @@
         <x:f>S178*T178</x:f>
       </x:c>
     </x:row>
-    <x:row r="179" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="179" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A179" s="87">
         <x:v>720482</x:v>
       </x:c>
@@ -10002,7 +10002,7 @@
         <x:f>S179*T179</x:f>
       </x:c>
     </x:row>
-    <x:row r="180" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="180" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A180" s="87">
         <x:v>720487</x:v>
       </x:c>
@@ -10042,7 +10042,7 @@
         <x:f>S180*T180</x:f>
       </x:c>
     </x:row>
-    <x:row r="181" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="181" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A181" s="87">
         <x:v>720487</x:v>
       </x:c>
@@ -10082,7 +10082,7 @@
         <x:f>S181*T181</x:f>
       </x:c>
     </x:row>
-    <x:row r="182" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="182" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A182" s="87">
         <x:v>720487</x:v>
       </x:c>
@@ -10122,7 +10122,7 @@
         <x:f>S182*T182</x:f>
       </x:c>
     </x:row>
-    <x:row r="183" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="183" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A183" s="87">
         <x:v>720488</x:v>
       </x:c>
@@ -10162,7 +10162,7 @@
         <x:f>S183*T183</x:f>
       </x:c>
     </x:row>
-    <x:row r="184" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="184" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A184" s="87">
         <x:v>720488</x:v>
       </x:c>
@@ -10202,7 +10202,7 @@
         <x:f>S184*T184</x:f>
       </x:c>
     </x:row>
-    <x:row r="185" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="185" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A185" s="87">
         <x:v>720488</x:v>
       </x:c>
@@ -10242,7 +10242,7 @@
         <x:f>S185*T185</x:f>
       </x:c>
     </x:row>
-    <x:row r="186" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="186" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A186" s="87">
         <x:v>720491</x:v>
       </x:c>
@@ -10282,7 +10282,7 @@
         <x:f>S186*T186</x:f>
       </x:c>
     </x:row>
-    <x:row r="187" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="187" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A187" s="87">
         <x:v>720491</x:v>
       </x:c>
@@ -10322,7 +10322,7 @@
         <x:f>S187*T187</x:f>
       </x:c>
     </x:row>
-    <x:row r="188" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="188" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A188" s="87">
         <x:v>720492</x:v>
       </x:c>
@@ -10362,7 +10362,7 @@
         <x:f>S188*T188</x:f>
       </x:c>
     </x:row>
-    <x:row r="189" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="189" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A189" s="87">
         <x:v>720492</x:v>
       </x:c>
@@ -10402,7 +10402,7 @@
         <x:f>S189*T189</x:f>
       </x:c>
     </x:row>
-    <x:row r="190" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="190" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A190" s="87">
         <x:v>720498</x:v>
       </x:c>
@@ -10442,7 +10442,7 @@
         <x:f>S190*T190</x:f>
       </x:c>
     </x:row>
-    <x:row r="191" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="191" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A191" s="87">
         <x:v>720498</x:v>
       </x:c>
@@ -10482,7 +10482,7 @@
         <x:f>S191*T191</x:f>
       </x:c>
     </x:row>
-    <x:row r="192" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="192" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A192" s="87">
         <x:v>720498</x:v>
       </x:c>
@@ -10522,7 +10522,7 @@
         <x:f>S192*T192</x:f>
       </x:c>
     </x:row>
-    <x:row r="193" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="193" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A193" s="87">
         <x:v>720502</x:v>
       </x:c>
@@ -10562,7 +10562,7 @@
         <x:f>S193*T193</x:f>
       </x:c>
     </x:row>
-    <x:row r="194" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="194" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A194" s="87">
         <x:v>720502</x:v>
       </x:c>
@@ -10602,7 +10602,7 @@
         <x:f>S194*T194</x:f>
       </x:c>
     </x:row>
-    <x:row r="195" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="195" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A195" s="87">
         <x:v>720502</x:v>
       </x:c>
@@ -10642,7 +10642,7 @@
         <x:f>S195*T195</x:f>
       </x:c>
     </x:row>
-    <x:row r="196" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="196" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A196" s="87">
         <x:v>720502</x:v>
       </x:c>
@@ -10682,7 +10682,7 @@
         <x:f>S196*T196</x:f>
       </x:c>
     </x:row>
-    <x:row r="197" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="197" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A197" s="87">
         <x:v>720505</x:v>
       </x:c>
@@ -10722,7 +10722,7 @@
         <x:f>S197*T197</x:f>
       </x:c>
     </x:row>
-    <x:row r="198" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="198" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A198" s="87">
         <x:v>720505</x:v>
       </x:c>
@@ -10762,7 +10762,7 @@
         <x:f>S198*T198</x:f>
       </x:c>
     </x:row>
-    <x:row r="199" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="199" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A199" s="87">
         <x:v>720505</x:v>
       </x:c>
@@ -10802,7 +10802,7 @@
         <x:f>S199*T199</x:f>
       </x:c>
     </x:row>
-    <x:row r="200" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="200" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A200" s="87">
         <x:v>720506</x:v>
       </x:c>
@@ -10842,7 +10842,7 @@
         <x:f>S200*T200</x:f>
       </x:c>
     </x:row>
-    <x:row r="201" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="201" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A201" s="87">
         <x:v>720506</x:v>
       </x:c>
@@ -10882,7 +10882,7 @@
         <x:f>S201*T201</x:f>
       </x:c>
     </x:row>
-    <x:row r="202" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="202" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A202" s="87">
         <x:v>720506</x:v>
       </x:c>
@@ -10922,7 +10922,7 @@
         <x:f>S202*T202</x:f>
       </x:c>
     </x:row>
-    <x:row r="203" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="203" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A203" s="87">
         <x:v>720506</x:v>
       </x:c>
@@ -10962,7 +10962,7 @@
         <x:f>S203*T203</x:f>
       </x:c>
     </x:row>
-    <x:row r="204" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="204" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A204" s="87">
         <x:v>720506</x:v>
       </x:c>
@@ -11002,7 +11002,7 @@
         <x:f>S204*T204</x:f>
       </x:c>
     </x:row>
-    <x:row r="205" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="205" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A205" s="87">
         <x:v>720506</x:v>
       </x:c>
@@ -11042,7 +11042,7 @@
         <x:f>S205*T205</x:f>
       </x:c>
     </x:row>
-    <x:row r="206" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="206" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A206" s="87">
         <x:v>720509</x:v>
       </x:c>
@@ -11082,7 +11082,7 @@
         <x:f>S206*T206</x:f>
       </x:c>
     </x:row>
-    <x:row r="207" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="207" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A207" s="87">
         <x:v>720509</x:v>
       </x:c>
@@ -11122,7 +11122,7 @@
         <x:f>S207*T207</x:f>
       </x:c>
     </x:row>
-    <x:row r="208" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="208" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A208" s="87">
         <x:v>720509</x:v>
       </x:c>
@@ -11162,7 +11162,7 @@
         <x:f>S208*T208</x:f>
       </x:c>
     </x:row>
-    <x:row r="209" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="209" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A209" s="87">
         <x:v>720509</x:v>
       </x:c>
@@ -11202,7 +11202,7 @@
         <x:f>S209*T209</x:f>
       </x:c>
     </x:row>
-    <x:row r="210" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="210" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A210" s="87">
         <x:v>720515</x:v>
       </x:c>
@@ -11242,7 +11242,7 @@
         <x:f>S210*T210</x:f>
       </x:c>
     </x:row>
-    <x:row r="211" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="211" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A211" s="87">
         <x:v>720515</x:v>
       </x:c>
@@ -11282,7 +11282,7 @@
         <x:f>S211*T211</x:f>
       </x:c>
     </x:row>
-    <x:row r="212" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="212" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A212" s="87">
         <x:v>720515</x:v>
       </x:c>
@@ -11322,7 +11322,7 @@
         <x:f>S212*T212</x:f>
       </x:c>
     </x:row>
-    <x:row r="213" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="213" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A213" s="87">
         <x:v>720515</x:v>
       </x:c>
@@ -11362,7 +11362,7 @@
         <x:f>S213*T213</x:f>
       </x:c>
     </x:row>
-    <x:row r="214" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="214" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A214" s="87">
         <x:v>720517</x:v>
       </x:c>
@@ -11402,7 +11402,7 @@
         <x:f>S214*T214</x:f>
       </x:c>
     </x:row>
-    <x:row r="215" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="215" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A215" s="87">
         <x:v>720517</x:v>
       </x:c>
@@ -11442,7 +11442,7 @@
         <x:f>S215*T215</x:f>
       </x:c>
     </x:row>
-    <x:row r="216" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="216" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A216" s="87">
         <x:v>720517</x:v>
       </x:c>
@@ -11482,7 +11482,7 @@
         <x:f>S216*T216</x:f>
       </x:c>
     </x:row>
-    <x:row r="217" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="217" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A217" s="87">
         <x:v>720517</x:v>
       </x:c>
@@ -11522,7 +11522,7 @@
         <x:f>S217*T217</x:f>
       </x:c>
     </x:row>
-    <x:row r="218" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="218" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A218" s="87">
         <x:v>720519</x:v>
       </x:c>
@@ -11562,7 +11562,7 @@
         <x:f>S218*T218</x:f>
       </x:c>
     </x:row>
-    <x:row r="219" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="219" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A219" s="87">
         <x:v>720519</x:v>
       </x:c>
@@ -11602,7 +11602,7 @@
         <x:f>S219*T219</x:f>
       </x:c>
     </x:row>
-    <x:row r="220" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="220" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A220" s="87">
         <x:v>720521</x:v>
       </x:c>
@@ -11642,7 +11642,7 @@
         <x:f>S220*T220</x:f>
       </x:c>
     </x:row>
-    <x:row r="221" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="221" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A221" s="87">
         <x:v>720521</x:v>
       </x:c>
@@ -11682,7 +11682,7 @@
         <x:f>S221*T221</x:f>
       </x:c>
     </x:row>
-    <x:row r="222" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="222" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A222" s="87">
         <x:v>720523</x:v>
       </x:c>
@@ -11722,7 +11722,7 @@
         <x:f>S222*T222</x:f>
       </x:c>
     </x:row>
-    <x:row r="223" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="223" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A223" s="87">
         <x:v>720523</x:v>
       </x:c>
@@ -11762,7 +11762,7 @@
         <x:f>S223*T223</x:f>
       </x:c>
     </x:row>
-    <x:row r="224" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="224" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A224" s="87">
         <x:v>720523</x:v>
       </x:c>
@@ -11802,7 +11802,7 @@
         <x:f>S224*T224</x:f>
       </x:c>
     </x:row>
-    <x:row r="225" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="225" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A225" s="87">
         <x:v>720523</x:v>
       </x:c>
@@ -11842,7 +11842,7 @@
         <x:f>S225*T225</x:f>
       </x:c>
     </x:row>
-    <x:row r="226" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="226" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A226" s="87">
         <x:v>720523</x:v>
       </x:c>
@@ -11882,7 +11882,7 @@
         <x:f>S226*T226</x:f>
       </x:c>
     </x:row>
-    <x:row r="227" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="227" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A227" s="87">
         <x:v>720527</x:v>
       </x:c>
@@ -11922,7 +11922,7 @@
         <x:f>S227*T227</x:f>
       </x:c>
     </x:row>
-    <x:row r="228" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="228" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A228" s="87">
         <x:v>720527</x:v>
       </x:c>
@@ -11962,7 +11962,7 @@
         <x:f>S228*T228</x:f>
       </x:c>
     </x:row>
-    <x:row r="229" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="229" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A229" s="87">
         <x:v>720527</x:v>
       </x:c>
@@ -12002,7 +12002,7 @@
         <x:f>S229*T229</x:f>
       </x:c>
     </x:row>
-    <x:row r="230" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="230" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A230" s="87">
         <x:v>720529</x:v>
       </x:c>
@@ -12042,7 +12042,7 @@
         <x:f>S230*T230</x:f>
       </x:c>
     </x:row>
-    <x:row r="231" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="231" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A231" s="87">
         <x:v>720529</x:v>
       </x:c>
@@ -12082,7 +12082,7 @@
         <x:f>S231*T231</x:f>
       </x:c>
     </x:row>
-    <x:row r="232" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="232" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A232" s="87">
         <x:v>720529</x:v>
       </x:c>
@@ -12122,7 +12122,7 @@
         <x:f>S232*T232</x:f>
       </x:c>
     </x:row>
-    <x:row r="233" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="233" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A233" s="87">
         <x:v>743030</x:v>
       </x:c>
@@ -12162,7 +12162,7 @@
         <x:f>S233*T233</x:f>
       </x:c>
     </x:row>
-    <x:row r="234" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="234" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A234" s="87">
         <x:v>743030</x:v>
       </x:c>
@@ -12202,7 +12202,7 @@
         <x:f>S234*T234</x:f>
       </x:c>
     </x:row>
-    <x:row r="235" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="235" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A235" s="87"/>
       <x:c r="B235" s="87"/>
       <x:c r="C235" s="87"/>
@@ -12226,7 +12226,7 @@
       <x:c r="U235" s="88"/>
       <x:c r="V235" s="108"/>
     </x:row>
-    <x:row r="236" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="236" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A236" s="87"/>
       <x:c r="B236" s="87"/>
       <x:c r="C236" s="87"/>
@@ -12250,7 +12250,7 @@
       <x:c r="U236" s="88"/>
       <x:c r="V236" s="108"/>
     </x:row>
-    <x:row r="237" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="237" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A237" s="87"/>
       <x:c r="B237" s="87"/>
       <x:c r="C237" s="87"/>
@@ -12274,7 +12274,7 @@
       <x:c r="U237" s="88"/>
       <x:c r="V237" s="108"/>
     </x:row>
-    <x:row r="238" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="238" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A238" s="87"/>
       <x:c r="B238" s="87"/>
       <x:c r="C238" s="87"/>
@@ -12298,7 +12298,7 @@
       <x:c r="U238" s="88"/>
       <x:c r="V238" s="108"/>
     </x:row>
-    <x:row r="239" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="239" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A239" s="87">
         <x:v>743037</x:v>
       </x:c>
@@ -12338,7 +12338,7 @@
         <x:f>S239*T239</x:f>
       </x:c>
     </x:row>
-    <x:row r="240" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="240" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A240" s="87">
         <x:v>743037</x:v>
       </x:c>
@@ -12378,7 +12378,7 @@
         <x:f>S240*T240</x:f>
       </x:c>
     </x:row>
-    <x:row r="241" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="241" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A241" s="87">
         <x:v>743041</x:v>
       </x:c>
@@ -12418,7 +12418,7 @@
         <x:f>S241*T241</x:f>
       </x:c>
     </x:row>
-    <x:row r="242" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="242" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A242" s="87">
         <x:v>743041</x:v>
       </x:c>
@@ -12458,7 +12458,7 @@
         <x:f>S242*T242</x:f>
       </x:c>
     </x:row>
-    <x:row r="243" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="243" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A243" s="87">
         <x:v>743041</x:v>
       </x:c>
@@ -12498,7 +12498,7 @@
         <x:f>S243*T243</x:f>
       </x:c>
     </x:row>
-    <x:row r="244" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="244" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A244" s="87">
         <x:v>743049</x:v>
       </x:c>
@@ -12538,7 +12538,7 @@
         <x:f>S244*T244</x:f>
       </x:c>
     </x:row>
-    <x:row r="245" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="245" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A245" s="87"/>
       <x:c r="B245" s="87"/>
       <x:c r="C245" s="87"/>
@@ -12562,7 +12562,7 @@
       <x:c r="U245" s="88"/>
       <x:c r="V245" s="108"/>
     </x:row>
-    <x:row r="246" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="246" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A246" s="87"/>
       <x:c r="B246" s="87"/>
       <x:c r="C246" s="87"/>
@@ -12586,7 +12586,7 @@
       <x:c r="U246" s="88"/>
       <x:c r="V246" s="108"/>
     </x:row>
-    <x:row r="247" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="247" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A247" s="87"/>
       <x:c r="B247" s="87"/>
       <x:c r="C247" s="87"/>
@@ -12610,7 +12610,7 @@
       <x:c r="U247" s="88"/>
       <x:c r="V247" s="108"/>
     </x:row>
-    <x:row r="248" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="248" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A248" s="87">
         <x:v>743059</x:v>
       </x:c>
@@ -12650,7 +12650,7 @@
         <x:f>S248*T248</x:f>
       </x:c>
     </x:row>
-    <x:row r="249" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="249" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A249" s="87">
         <x:v>743059</x:v>
       </x:c>
@@ -12690,7 +12690,7 @@
         <x:f>S249*T249</x:f>
       </x:c>
     </x:row>
-    <x:row r="250" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="250" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A250" s="87">
         <x:v>743059</x:v>
       </x:c>
@@ -12730,7 +12730,7 @@
         <x:f>S250*T250</x:f>
       </x:c>
     </x:row>
-    <x:row r="251" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="251" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A251" s="87">
         <x:v>743059</x:v>
       </x:c>
@@ -12770,7 +12770,7 @@
         <x:f>S251*T251</x:f>
       </x:c>
     </x:row>
-    <x:row r="252" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="252" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A252" s="87">
         <x:v>743059</x:v>
       </x:c>
@@ -12810,7 +12810,7 @@
         <x:f>S252*T252</x:f>
       </x:c>
     </x:row>
-    <x:row r="253" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="253" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A253" s="87">
         <x:v>743059</x:v>
       </x:c>
@@ -12850,7 +12850,7 @@
         <x:f>S253*T253</x:f>
       </x:c>
     </x:row>
-    <x:row r="254" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="254" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A254" s="87">
         <x:v>743065</x:v>
       </x:c>
@@ -12890,7 +12890,7 @@
         <x:f>S254*T254</x:f>
       </x:c>
     </x:row>
-    <x:row r="255" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="255" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A255" s="87">
         <x:v>743065</x:v>
       </x:c>
@@ -12930,7 +12930,7 @@
         <x:f>S255*T255</x:f>
       </x:c>
     </x:row>
-    <x:row r="256" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="256" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A256" s="87">
         <x:v>743065</x:v>
       </x:c>
@@ -12970,7 +12970,7 @@
         <x:f>S256*T256</x:f>
       </x:c>
     </x:row>
-    <x:row r="257" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="257" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A257" s="87">
         <x:v>743068</x:v>
       </x:c>
@@ -13010,7 +13010,7 @@
         <x:f>S257*T257</x:f>
       </x:c>
     </x:row>
-    <x:row r="258" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="258" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A258" s="87">
         <x:v>743069</x:v>
       </x:c>
@@ -13050,7 +13050,7 @@
         <x:f>S258*T258</x:f>
       </x:c>
     </x:row>
-    <x:row r="259" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="259" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A259" s="87">
         <x:v>743073</x:v>
       </x:c>
@@ -13090,7 +13090,7 @@
         <x:f>S259*T259</x:f>
       </x:c>
     </x:row>
-    <x:row r="260" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="260" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A260" s="87">
         <x:v>743073</x:v>
       </x:c>
@@ -13130,7 +13130,7 @@
         <x:f>S260*T260</x:f>
       </x:c>
     </x:row>
-    <x:row r="261" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="261" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A261" s="87">
         <x:v>743073</x:v>
       </x:c>
@@ -13170,7 +13170,7 @@
         <x:f>S261*T261</x:f>
       </x:c>
     </x:row>
-    <x:row r="262" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="262" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A262" s="87">
         <x:v>743077</x:v>
       </x:c>
@@ -13210,7 +13210,7 @@
         <x:f>S262*T262</x:f>
       </x:c>
     </x:row>
-    <x:row r="263" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="263" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A263" s="87">
         <x:v>743077</x:v>
       </x:c>
@@ -13250,7 +13250,7 @@
         <x:f>S263*T263</x:f>
       </x:c>
     </x:row>
-    <x:row r="264" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="264" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A264" s="87">
         <x:v>743079</x:v>
       </x:c>
@@ -13290,7 +13290,7 @@
         <x:f>S264*T264</x:f>
       </x:c>
     </x:row>
-    <x:row r="265" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="265" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A265" s="87">
         <x:v>743079</x:v>
       </x:c>
@@ -13330,7 +13330,7 @@
         <x:f>S265*T265</x:f>
       </x:c>
     </x:row>
-    <x:row r="266" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="266" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A266" s="87">
         <x:v>743079</x:v>
       </x:c>
@@ -13370,7 +13370,7 @@
         <x:f>S266*T266</x:f>
       </x:c>
     </x:row>
-    <x:row r="267" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="267" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A267" s="87"/>
       <x:c r="B267" s="87"/>
       <x:c r="C267" s="87"/>
@@ -13394,7 +13394,7 @@
       <x:c r="U267" s="88"/>
       <x:c r="V267" s="108"/>
     </x:row>
-    <x:row r="268" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="268" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A268" s="87">
         <x:v>743087</x:v>
       </x:c>
@@ -13434,7 +13434,7 @@
         <x:f>S268*T268</x:f>
       </x:c>
     </x:row>
-    <x:row r="269" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="269" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A269" s="87">
         <x:v>743087</x:v>
       </x:c>
@@ -13474,7 +13474,7 @@
         <x:f>S269*T269</x:f>
       </x:c>
     </x:row>
-    <x:row r="270" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="270" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A270" s="87">
         <x:v>743087</x:v>
       </x:c>
@@ -13514,7 +13514,7 @@
         <x:f>S270*T270</x:f>
       </x:c>
     </x:row>
-    <x:row r="271" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="271" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A271" s="87">
         <x:v>743087</x:v>
       </x:c>
@@ -13554,7 +13554,7 @@
         <x:f>S271*T271</x:f>
       </x:c>
     </x:row>
-    <x:row r="272" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="272" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A272" s="87">
         <x:v>743087</x:v>
       </x:c>
@@ -13594,7 +13594,7 @@
         <x:f>S272*T272</x:f>
       </x:c>
     </x:row>
-    <x:row r="273" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="273" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A273" s="87">
         <x:v>743091</x:v>
       </x:c>
@@ -13634,7 +13634,7 @@
         <x:f>S273*T273</x:f>
       </x:c>
     </x:row>
-    <x:row r="274" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="274" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A274" s="87">
         <x:v>743091</x:v>
       </x:c>
@@ -13674,7 +13674,7 @@
         <x:f>S274*T274</x:f>
       </x:c>
     </x:row>
-    <x:row r="275" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="275" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A275" s="87">
         <x:v>743093</x:v>
       </x:c>
@@ -13714,7 +13714,7 @@
         <x:f>S275*T275</x:f>
       </x:c>
     </x:row>
-    <x:row r="276" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="276" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A276" s="87">
         <x:v>743093</x:v>
       </x:c>
@@ -13754,7 +13754,7 @@
         <x:f>S276*T276</x:f>
       </x:c>
     </x:row>
-    <x:row r="277" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="277" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A277" s="87">
         <x:v>743093</x:v>
       </x:c>
@@ -13794,7 +13794,7 @@
         <x:f>S277*T277</x:f>
       </x:c>
     </x:row>
-    <x:row r="278" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="278" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A278" s="87">
         <x:v>743093</x:v>
       </x:c>
@@ -13834,7 +13834,7 @@
         <x:f>S278*T278</x:f>
       </x:c>
     </x:row>
-    <x:row r="279" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="279" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A279" s="87">
         <x:v>743093</x:v>
       </x:c>
@@ -13874,7 +13874,7 @@
         <x:f>S279*T279</x:f>
       </x:c>
     </x:row>
-    <x:row r="280" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="280" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A280" s="87"/>
       <x:c r="B280" s="87"/>
       <x:c r="C280" s="87"/>
@@ -13898,7 +13898,7 @@
       <x:c r="U280" s="88"/>
       <x:c r="V280" s="108"/>
     </x:row>
-    <x:row r="281" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="281" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A281" s="87"/>
       <x:c r="B281" s="87"/>
       <x:c r="C281" s="87"/>
@@ -13922,7 +13922,7 @@
       <x:c r="U281" s="88"/>
       <x:c r="V281" s="108"/>
     </x:row>
-    <x:row r="282" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="282" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A282" s="87">
         <x:v>743097</x:v>
       </x:c>
@@ -13962,7 +13962,7 @@
         <x:f>S282*T282</x:f>
       </x:c>
     </x:row>
-    <x:row r="283" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="283" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A283" s="87">
         <x:v>743097</x:v>
       </x:c>
@@ -14002,7 +14002,7 @@
         <x:f>S283*T283</x:f>
       </x:c>
     </x:row>
-    <x:row r="284" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="284" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A284" s="87">
         <x:v>743097</x:v>
       </x:c>
@@ -14042,7 +14042,7 @@
         <x:f>S284*T284</x:f>
       </x:c>
     </x:row>
-    <x:row r="285" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="285" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A285" s="87">
         <x:v>743098</x:v>
       </x:c>
@@ -14082,7 +14082,7 @@
         <x:f>S285*T285</x:f>
       </x:c>
     </x:row>
-    <x:row r="286" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="286" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A286" s="87">
         <x:v>743098</x:v>
       </x:c>
@@ -14122,7 +14122,7 @@
         <x:f>S286*T286</x:f>
       </x:c>
     </x:row>
-    <x:row r="287" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="287" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A287" s="87">
         <x:v>743103</x:v>
       </x:c>
@@ -14162,7 +14162,7 @@
         <x:f>S287*T287</x:f>
       </x:c>
     </x:row>
-    <x:row r="288" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="288" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A288" s="87">
         <x:v>743105</x:v>
       </x:c>
@@ -14202,7 +14202,7 @@
         <x:f>S288*T288</x:f>
       </x:c>
     </x:row>
-    <x:row r="289" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="289" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A289" s="87">
         <x:v>743105</x:v>
       </x:c>
@@ -14242,7 +14242,7 @@
         <x:f>S289*T289</x:f>
       </x:c>
     </x:row>
-    <x:row r="290" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="290" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A290" s="87">
         <x:v>743107</x:v>
       </x:c>
@@ -14282,7 +14282,7 @@
         <x:f>S290*T290</x:f>
       </x:c>
     </x:row>
-    <x:row r="291" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="291" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A291" s="87">
         <x:v>743107</x:v>
       </x:c>
@@ -14322,7 +14322,7 @@
         <x:f>S291*T291</x:f>
       </x:c>
     </x:row>
-    <x:row r="292" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="292" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A292" s="87">
         <x:v>743109</x:v>
       </x:c>
@@ -14362,7 +14362,7 @@
         <x:f>S292*T292</x:f>
       </x:c>
     </x:row>
-    <x:row r="293" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="293" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A293" s="87"/>
       <x:c r="B293" s="87"/>
       <x:c r="C293" s="87"/>
@@ -14386,7 +14386,7 @@
       <x:c r="U293" s="88"/>
       <x:c r="V293" s="108"/>
     </x:row>
-    <x:row r="294" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="294" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A294" s="87">
         <x:v>743109</x:v>
       </x:c>
@@ -14426,7 +14426,7 @@
         <x:f>S294*T294</x:f>
       </x:c>
     </x:row>
-    <x:row r="295" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="295" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A295" s="87">
         <x:v>743109</x:v>
       </x:c>
@@ -14466,7 +14466,7 @@
         <x:f>S295*T295</x:f>
       </x:c>
     </x:row>
-    <x:row r="296" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="296" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A296" s="87"/>
       <x:c r="B296" s="87"/>
       <x:c r="C296" s="87"/>
@@ -14490,7 +14490,7 @@
       <x:c r="U296" s="88"/>
       <x:c r="V296" s="108"/>
     </x:row>
-    <x:row r="297" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="297" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A297" s="87">
         <x:v>743109</x:v>
       </x:c>
@@ -14530,7 +14530,7 @@
         <x:f>S297*T297</x:f>
       </x:c>
     </x:row>
-    <x:row r="298" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="298" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A298" s="87">
         <x:v>743111</x:v>
       </x:c>
@@ -14570,7 +14570,7 @@
         <x:f>S298*T298</x:f>
       </x:c>
     </x:row>
-    <x:row r="299" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="299" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A299" s="87">
         <x:v>743111</x:v>
       </x:c>
@@ -14610,7 +14610,7 @@
         <x:f>S299*T299</x:f>
       </x:c>
     </x:row>
-    <x:row r="300" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="300" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A300" s="87">
         <x:v>743113</x:v>
       </x:c>
@@ -14650,7 +14650,7 @@
         <x:f>S300*T300</x:f>
       </x:c>
     </x:row>
-    <x:row r="301" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="301" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A301" s="87">
         <x:v>743113</x:v>
       </x:c>
@@ -14690,7 +14690,7 @@
         <x:f>S301*T301</x:f>
       </x:c>
     </x:row>
-    <x:row r="302" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="302" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A302" s="87">
         <x:v>743115</x:v>
       </x:c>
@@ -14730,7 +14730,7 @@
         <x:f>S302*T302</x:f>
       </x:c>
     </x:row>
-    <x:row r="303" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="303" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A303" s="87">
         <x:v>743115</x:v>
       </x:c>
@@ -14770,7 +14770,7 @@
         <x:f>S303*T303</x:f>
       </x:c>
     </x:row>
-    <x:row r="304" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="304" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A304" s="87">
         <x:v>743117</x:v>
       </x:c>
@@ -14810,7 +14810,7 @@
         <x:f>S304*T304</x:f>
       </x:c>
     </x:row>
-    <x:row r="305" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="305" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A305" s="87">
         <x:v>743117</x:v>
       </x:c>
@@ -14850,7 +14850,7 @@
         <x:f>S305*T305</x:f>
       </x:c>
     </x:row>
-    <x:row r="306" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="306" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A306" s="87">
         <x:v>743117</x:v>
       </x:c>
@@ -14890,7 +14890,7 @@
         <x:f>S306*T306</x:f>
       </x:c>
     </x:row>
-    <x:row r="307" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="307" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A307" s="87">
         <x:v>743117</x:v>
       </x:c>
@@ -14930,7 +14930,7 @@
         <x:f>S307*T307</x:f>
       </x:c>
     </x:row>
-    <x:row r="308" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="308" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A308" s="87">
         <x:v>743117</x:v>
       </x:c>
@@ -14970,7 +14970,7 @@
         <x:f>S308*T308</x:f>
       </x:c>
     </x:row>
-    <x:row r="309" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="309" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A309" s="87">
         <x:v>743117</x:v>
       </x:c>
@@ -15010,7 +15010,7 @@
         <x:f>S309*T309</x:f>
       </x:c>
     </x:row>
-    <x:row r="310" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="310" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A310" s="87">
         <x:v>743121</x:v>
       </x:c>
@@ -15050,7 +15050,7 @@
         <x:f>S310*T310</x:f>
       </x:c>
     </x:row>
-    <x:row r="311" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="311" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A311" s="87">
         <x:v>743121</x:v>
       </x:c>
@@ -15090,7 +15090,7 @@
         <x:f>S311*T311</x:f>
       </x:c>
     </x:row>
-    <x:row r="312" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="312" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A312" s="87">
         <x:v>743129</x:v>
       </x:c>
@@ -15130,7 +15130,7 @@
         <x:f>S312*T312</x:f>
       </x:c>
     </x:row>
-    <x:row r="313" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="313" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A313" s="87">
         <x:v>743129</x:v>
       </x:c>
@@ -15170,7 +15170,7 @@
         <x:f>S313*T313</x:f>
       </x:c>
     </x:row>
-    <x:row r="314" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="314" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A314" s="87">
         <x:v>743133</x:v>
       </x:c>
@@ -15210,7 +15210,7 @@
         <x:f>S314*T314</x:f>
       </x:c>
     </x:row>
-    <x:row r="315" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="315" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A315" s="87">
         <x:v>743133</x:v>
       </x:c>
@@ -15250,7 +15250,7 @@
         <x:f>S315*T315</x:f>
       </x:c>
     </x:row>
-    <x:row r="316" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="316" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A316" s="87">
         <x:v>743133</x:v>
       </x:c>
@@ -15290,7 +15290,7 @@
         <x:f>S316*T316</x:f>
       </x:c>
     </x:row>
-    <x:row r="317" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="317" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A317" s="87">
         <x:v>743133</x:v>
       </x:c>
@@ -15330,7 +15330,7 @@
         <x:f>S317*T317</x:f>
       </x:c>
     </x:row>
-    <x:row r="318" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="318" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A318" s="87">
         <x:v>743134</x:v>
       </x:c>
@@ -15370,7 +15370,7 @@
         <x:f>S318*T318</x:f>
       </x:c>
     </x:row>
-    <x:row r="319" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="319" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A319" s="87">
         <x:v>743134</x:v>
       </x:c>
@@ -15410,7 +15410,7 @@
         <x:f>S319*T319</x:f>
       </x:c>
     </x:row>
-    <x:row r="320" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="320" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A320" s="87">
         <x:v>743134</x:v>
       </x:c>
@@ -15450,7 +15450,7 @@
         <x:f>S320*T320</x:f>
       </x:c>
     </x:row>
-    <x:row r="321" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="321" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A321" s="87">
         <x:v>743134</x:v>
       </x:c>
@@ -15490,7 +15490,7 @@
         <x:f>S321*T321</x:f>
       </x:c>
     </x:row>
-    <x:row r="322" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="322" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A322" s="87">
         <x:v>743135</x:v>
       </x:c>
@@ -15530,7 +15530,7 @@
         <x:f>S322*T322</x:f>
       </x:c>
     </x:row>
-    <x:row r="323" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="323" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A323" s="87">
         <x:v>743135</x:v>
       </x:c>
@@ -15570,7 +15570,7 @@
         <x:f>S323*T323</x:f>
       </x:c>
     </x:row>
-    <x:row r="324" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="324" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A324" s="87">
         <x:v>743135</x:v>
       </x:c>
@@ -15610,7 +15610,7 @@
         <x:f>S324*T324</x:f>
       </x:c>
     </x:row>
-    <x:row r="325" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="325" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A325" s="87">
         <x:v>743136</x:v>
       </x:c>
@@ -15650,7 +15650,7 @@
         <x:f>S325*T325</x:f>
       </x:c>
     </x:row>
-    <x:row r="326" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="326" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A326" s="87">
         <x:v>743136</x:v>
       </x:c>
@@ -15690,7 +15690,7 @@
         <x:f>S326*T326</x:f>
       </x:c>
     </x:row>
-    <x:row r="327" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="327" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A327" s="87">
         <x:v>743136</x:v>
       </x:c>
@@ -15730,7 +15730,7 @@
         <x:f>S327*T327</x:f>
       </x:c>
     </x:row>
-    <x:row r="328" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="328" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A328" s="87">
         <x:v>743136</x:v>
       </x:c>
@@ -15770,7 +15770,7 @@
         <x:f>S328*T328</x:f>
       </x:c>
     </x:row>
-    <x:row r="329" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="329" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A329" s="87">
         <x:v>743139</x:v>
       </x:c>
@@ -15810,7 +15810,7 @@
         <x:f>S329*T329</x:f>
       </x:c>
     </x:row>
-    <x:row r="330" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="330" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A330" s="87">
         <x:v>743139</x:v>
       </x:c>
@@ -15850,7 +15850,7 @@
         <x:f>S330*T330</x:f>
       </x:c>
     </x:row>
-    <x:row r="331" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="331" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A331" s="87">
         <x:v>743139</x:v>
       </x:c>
@@ -15890,7 +15890,7 @@
         <x:f>S331*T331</x:f>
       </x:c>
     </x:row>
-    <x:row r="332" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="332" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A332" s="87">
         <x:v>743139</x:v>
       </x:c>
@@ -15930,7 +15930,7 @@
         <x:f>S332*T332</x:f>
       </x:c>
     </x:row>
-    <x:row r="333" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="333" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A333" s="87">
         <x:v>743139</x:v>
       </x:c>
@@ -15970,7 +15970,7 @@
         <x:f>S333*T333</x:f>
       </x:c>
     </x:row>
-    <x:row r="334" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="334" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A334" s="87">
         <x:v>743139</x:v>
       </x:c>
@@ -16010,7 +16010,7 @@
         <x:f>S334*T334</x:f>
       </x:c>
     </x:row>
-    <x:row r="335" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="335" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A335" s="87">
         <x:v>743139</x:v>
       </x:c>
@@ -16050,7 +16050,7 @@
         <x:f>S335*T335</x:f>
       </x:c>
     </x:row>
-    <x:row r="336" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="336" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A336" s="87">
         <x:v>743139</x:v>
       </x:c>
@@ -16090,7 +16090,7 @@
         <x:f>S336*T336</x:f>
       </x:c>
     </x:row>
-    <x:row r="337" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="337" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A337" s="87">
         <x:v>743144</x:v>
       </x:c>
@@ -16130,7 +16130,7 @@
         <x:f>S337*T337</x:f>
       </x:c>
     </x:row>
-    <x:row r="338" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="338" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A338" s="87">
         <x:v>743144</x:v>
       </x:c>
@@ -16170,7 +16170,7 @@
         <x:f>S338*T338</x:f>
       </x:c>
     </x:row>
-    <x:row r="339" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="339" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A339" s="87">
         <x:v>743145</x:v>
       </x:c>
@@ -16210,7 +16210,7 @@
         <x:f>S339*T339</x:f>
       </x:c>
     </x:row>
-    <x:row r="340" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="340" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A340" s="87">
         <x:v>743145</x:v>
       </x:c>
@@ -16250,7 +16250,7 @@
         <x:f>S340*T340</x:f>
       </x:c>
     </x:row>
-    <x:row r="341" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="341" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A341" s="87">
         <x:v>743146</x:v>
       </x:c>
@@ -16290,7 +16290,7 @@
         <x:f>S341*T341</x:f>
       </x:c>
     </x:row>
-    <x:row r="342" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="342" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A342" s="87">
         <x:v>743147</x:v>
       </x:c>
@@ -16330,7 +16330,7 @@
         <x:f>S342*T342</x:f>
       </x:c>
     </x:row>
-    <x:row r="343" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="343" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A343" s="87">
         <x:v>743150</x:v>
       </x:c>
@@ -16370,7 +16370,7 @@
         <x:f>S343*T343</x:f>
       </x:c>
     </x:row>
-    <x:row r="344" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="344" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A344" s="87">
         <x:v>743150</x:v>
       </x:c>
@@ -16410,7 +16410,7 @@
         <x:f>S344*T344</x:f>
       </x:c>
     </x:row>
-    <x:row r="345" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="345" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A345" s="87">
         <x:v>743152</x:v>
       </x:c>
@@ -16450,7 +16450,7 @@
         <x:f>S345*T345</x:f>
       </x:c>
     </x:row>
-    <x:row r="346" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="346" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A346" s="87">
         <x:v>743152</x:v>
       </x:c>
@@ -16490,7 +16490,7 @@
         <x:f>S346*T346</x:f>
       </x:c>
     </x:row>
-    <x:row r="347" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="347" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A347" s="87">
         <x:v>743153</x:v>
       </x:c>
@@ -16530,7 +16530,7 @@
         <x:f>S347*T347</x:f>
       </x:c>
     </x:row>
-    <x:row r="348" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="348" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A348" s="87">
         <x:v>743153</x:v>
       </x:c>
@@ -16570,7 +16570,7 @@
         <x:f>S348*T348</x:f>
       </x:c>
     </x:row>
-    <x:row r="349" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="349" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A349" s="87">
         <x:v>743154</x:v>
       </x:c>
@@ -16610,7 +16610,7 @@
         <x:f>S349*T349</x:f>
       </x:c>
     </x:row>
-    <x:row r="350" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="350" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A350" s="87">
         <x:v>743154</x:v>
       </x:c>
@@ -16650,7 +16650,7 @@
         <x:f>S350*T350</x:f>
       </x:c>
     </x:row>
-    <x:row r="351" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="351" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A351" s="87">
         <x:v>743157</x:v>
       </x:c>
@@ -16690,7 +16690,7 @@
         <x:f>S351*T351</x:f>
       </x:c>
     </x:row>
-    <x:row r="352" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="352" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A352" s="87">
         <x:v>743157</x:v>
       </x:c>
@@ -16730,7 +16730,7 @@
         <x:f>S352*T352</x:f>
       </x:c>
     </x:row>
-    <x:row r="353" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="353" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A353" s="87">
         <x:v>743157</x:v>
       </x:c>
@@ -16770,7 +16770,7 @@
         <x:f>S353*T353</x:f>
       </x:c>
     </x:row>
-    <x:row r="354" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="354" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A354" s="87">
         <x:v>743158</x:v>
       </x:c>
@@ -16810,7 +16810,7 @@
         <x:f>S354*T354</x:f>
       </x:c>
     </x:row>
-    <x:row r="355" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="355" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A355" s="87">
         <x:v>743161</x:v>
       </x:c>
@@ -16850,7 +16850,7 @@
         <x:f>S355*T355</x:f>
       </x:c>
     </x:row>
-    <x:row r="356" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="356" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A356" s="87">
         <x:v>743161</x:v>
       </x:c>
@@ -16890,7 +16890,7 @@
         <x:f>S356*T356</x:f>
       </x:c>
     </x:row>
-    <x:row r="357" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="357" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A357" s="87">
         <x:v>743161</x:v>
       </x:c>
@@ -16930,7 +16930,7 @@
         <x:f>S357*T357</x:f>
       </x:c>
     </x:row>
-    <x:row r="358" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="358" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A358" s="87">
         <x:v>743164</x:v>
       </x:c>
@@ -16970,7 +16970,7 @@
         <x:f>S358*T358</x:f>
       </x:c>
     </x:row>
-    <x:row r="359" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="359" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A359" s="87">
         <x:v>743164</x:v>
       </x:c>
@@ -17010,7 +17010,7 @@
         <x:f>S359*T359</x:f>
       </x:c>
     </x:row>
-    <x:row r="360" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="360" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A360" s="87">
         <x:v>743165</x:v>
       </x:c>
@@ -17050,7 +17050,7 @@
         <x:f>S360*T360</x:f>
       </x:c>
     </x:row>
-    <x:row r="361" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="361" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A361" s="87">
         <x:v>743165</x:v>
       </x:c>
@@ -17090,7 +17090,7 @@
         <x:f>S361*T361</x:f>
       </x:c>
     </x:row>
-    <x:row r="362" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="362" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A362" s="87">
         <x:v>743165</x:v>
       </x:c>
@@ -17130,7 +17130,7 @@
         <x:f>S362*T362</x:f>
       </x:c>
     </x:row>
-    <x:row r="363" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="363" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A363" s="87">
         <x:v>743168</x:v>
       </x:c>
@@ -17170,7 +17170,7 @@
         <x:f>S363*T363</x:f>
       </x:c>
     </x:row>
-    <x:row r="364" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="364" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A364" s="87">
         <x:v>743168</x:v>
       </x:c>
@@ -17210,7 +17210,7 @@
         <x:f>S364*T364</x:f>
       </x:c>
     </x:row>
-    <x:row r="365" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="365" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A365" s="87">
         <x:v>743170</x:v>
       </x:c>
@@ -17250,7 +17250,7 @@
         <x:f>S365*T365</x:f>
       </x:c>
     </x:row>
-    <x:row r="366" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="366" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A366" s="87">
         <x:v>743170</x:v>
       </x:c>
@@ -17290,7 +17290,7 @@
         <x:f>S366*T366</x:f>
       </x:c>
     </x:row>
-    <x:row r="367" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="367" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A367" s="87">
         <x:v>743170</x:v>
       </x:c>
@@ -17330,7 +17330,7 @@
         <x:f>S367*T367</x:f>
       </x:c>
     </x:row>
-    <x:row r="368" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="368" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A368" s="87">
         <x:v>743170</x:v>
       </x:c>
@@ -17370,7 +17370,7 @@
         <x:f>S368*T368</x:f>
       </x:c>
     </x:row>
-    <x:row r="369" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="369" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A369" s="87">
         <x:v>743170</x:v>
       </x:c>
@@ -17410,7 +17410,7 @@
         <x:f>S369*T369</x:f>
       </x:c>
     </x:row>
-    <x:row r="370" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="370" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A370" s="87">
         <x:v>743172</x:v>
       </x:c>
@@ -17450,7 +17450,7 @@
         <x:f>S370*T370</x:f>
       </x:c>
     </x:row>
-    <x:row r="371" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="371" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A371" s="87">
         <x:v>743172</x:v>
       </x:c>
@@ -17490,7 +17490,7 @@
         <x:f>S371*T371</x:f>
       </x:c>
     </x:row>
-    <x:row r="372" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="372" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A372" s="87">
         <x:v>743174</x:v>
       </x:c>
@@ -17530,7 +17530,7 @@
         <x:f>S372*T372</x:f>
       </x:c>
     </x:row>
-    <x:row r="373" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="373" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A373" s="87">
         <x:v>743174</x:v>
       </x:c>
@@ -17570,7 +17570,7 @@
         <x:f>S373*T373</x:f>
       </x:c>
     </x:row>
-    <x:row r="374" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="374" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A374" s="87">
         <x:v>743176</x:v>
       </x:c>
@@ -17610,7 +17610,7 @@
         <x:f>S374*T374</x:f>
       </x:c>
     </x:row>
-    <x:row r="375" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="375" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A375" s="87">
         <x:v>743176</x:v>
       </x:c>
@@ -17650,7 +17650,7 @@
         <x:f>S375*T375</x:f>
       </x:c>
     </x:row>
-    <x:row r="376" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="376" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A376" s="87">
         <x:v>743176</x:v>
       </x:c>
@@ -17690,7 +17690,7 @@
         <x:f>S376*T376</x:f>
       </x:c>
     </x:row>
-    <x:row r="377" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="377" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A377" s="87">
         <x:v>743177</x:v>
       </x:c>
@@ -17730,7 +17730,7 @@
         <x:f>S377*T377</x:f>
       </x:c>
     </x:row>
-    <x:row r="378" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="378" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A378" s="87">
         <x:v>743177</x:v>
       </x:c>
@@ -17770,7 +17770,7 @@
         <x:f>S378*T378</x:f>
       </x:c>
     </x:row>
-    <x:row r="379" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="379" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A379" s="87">
         <x:v>743177</x:v>
       </x:c>
@@ -17810,7 +17810,7 @@
         <x:f>S379*T379</x:f>
       </x:c>
     </x:row>
-    <x:row r="380" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="380" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A380" s="87">
         <x:v>743177</x:v>
       </x:c>
@@ -17850,7 +17850,7 @@
         <x:f>S380*T380</x:f>
       </x:c>
     </x:row>
-    <x:row r="381" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="381" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A381" s="87">
         <x:v>743177</x:v>
       </x:c>
@@ -17890,7 +17890,7 @@
         <x:f>S381*T381</x:f>
       </x:c>
     </x:row>
-    <x:row r="382" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="382" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A382" s="87">
         <x:v>743179</x:v>
       </x:c>
@@ -17930,7 +17930,7 @@
         <x:f>S382*T382</x:f>
       </x:c>
     </x:row>
-    <x:row r="383" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="383" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A383" s="87">
         <x:v>743179</x:v>
       </x:c>
@@ -17970,7 +17970,7 @@
         <x:f>S383*T383</x:f>
       </x:c>
     </x:row>
-    <x:row r="384" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="384" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A384" s="87">
         <x:v>743183</x:v>
       </x:c>
@@ -18010,7 +18010,7 @@
         <x:f>S384*T384</x:f>
       </x:c>
     </x:row>
-    <x:row r="385" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="385" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A385" s="87">
         <x:v>743183</x:v>
       </x:c>
@@ -18050,7 +18050,7 @@
         <x:f>S385*T385</x:f>
       </x:c>
     </x:row>
-    <x:row r="386" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="386" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A386" s="87">
         <x:v>743183</x:v>
       </x:c>
@@ -18090,7 +18090,7 @@
         <x:f>S386*T386</x:f>
       </x:c>
     </x:row>
-    <x:row r="387" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="387" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A387" s="87">
         <x:v>743185</x:v>
       </x:c>
@@ -18130,7 +18130,7 @@
         <x:f>S387*T387</x:f>
       </x:c>
     </x:row>
-    <x:row r="388" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="388" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A388" s="87">
         <x:v>743185</x:v>
       </x:c>
@@ -18170,7 +18170,7 @@
         <x:f>S388*T388</x:f>
       </x:c>
     </x:row>
-    <x:row r="389" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="389" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A389" s="87">
         <x:v>743185</x:v>
       </x:c>
@@ -18210,7 +18210,7 @@
         <x:f>S389*T389</x:f>
       </x:c>
     </x:row>
-    <x:row r="390" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="390" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A390" s="87">
         <x:v>743187</x:v>
       </x:c>
@@ -18250,7 +18250,7 @@
         <x:f>S390*T390</x:f>
       </x:c>
     </x:row>
-    <x:row r="391" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="391" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A391" s="87">
         <x:v>743187</x:v>
       </x:c>
@@ -18290,7 +18290,7 @@
         <x:f>S391*T391</x:f>
       </x:c>
     </x:row>
-    <x:row r="392" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="392" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A392" s="87">
         <x:v>743188</x:v>
       </x:c>
@@ -18330,7 +18330,7 @@
         <x:f>S392*T392</x:f>
       </x:c>
     </x:row>
-    <x:row r="393" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="393" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A393" s="87">
         <x:v>743188</x:v>
       </x:c>
@@ -18370,7 +18370,7 @@
         <x:f>S393*T393</x:f>
       </x:c>
     </x:row>
-    <x:row r="394" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="394" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A394" s="87">
         <x:v>743189</x:v>
       </x:c>
@@ -18410,7 +18410,7 @@
         <x:f>S394*T394</x:f>
       </x:c>
     </x:row>
-    <x:row r="395" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="395" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A395" s="87">
         <x:v>743189</x:v>
       </x:c>
@@ -18450,7 +18450,7 @@
         <x:f>S395*T395</x:f>
       </x:c>
     </x:row>
-    <x:row r="396" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="396" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A396" s="87">
         <x:v>760401</x:v>
       </x:c>
@@ -18490,7 +18490,7 @@
         <x:f>S396*T396</x:f>
       </x:c>
     </x:row>
-    <x:row r="397" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="397" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A397" s="87">
         <x:v>760401</x:v>
       </x:c>
@@ -18530,7 +18530,7 @@
         <x:f>S397*T397</x:f>
       </x:c>
     </x:row>
-    <x:row r="398" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="398" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A398" s="87">
         <x:v>760401</x:v>
       </x:c>
@@ -18570,7 +18570,7 @@
         <x:f>S398*T398</x:f>
       </x:c>
     </x:row>
-    <x:row r="399" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="399" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A399" s="87">
         <x:v>760401</x:v>
       </x:c>
@@ -18610,7 +18610,7 @@
         <x:f>S399*T399</x:f>
       </x:c>
     </x:row>
-    <x:row r="400" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="400" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A400" s="87"/>
       <x:c r="B400" s="87"/>
       <x:c r="C400" s="87"/>
@@ -18634,7 +18634,7 @@
       <x:c r="U400" s="88"/>
       <x:c r="V400" s="108"/>
     </x:row>
-    <x:row r="401" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="401" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A401" s="87"/>
       <x:c r="B401" s="87"/>
       <x:c r="C401" s="87"/>
@@ -18658,7 +18658,7 @@
       <x:c r="U401" s="88"/>
       <x:c r="V401" s="108"/>
     </x:row>
-    <x:row r="402" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="402" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A402" s="87">
         <x:v>760403</x:v>
       </x:c>
@@ -18698,7 +18698,7 @@
         <x:f>S402*T402</x:f>
       </x:c>
     </x:row>
-    <x:row r="403" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <x:row r="403" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <x:c r="A403" s="87"/>
       <x:c r="B403" s="87"/>
       <x:c r="C403" s="87"/>
@@ -18722,7 +18722,7 @@
       <x:c r="U403" s="88"/>
       <x:c r="V403" s="108"/>
     </x:row>
-    <x:row r="404" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="404" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A404" s="87">
         <x:v>760405</x:v>
       </x:c>
@@ -18762,7 +18762,7 @@
         <x:f>S404*T404</x:f>
       </x:c>
     </x:row>
-    <x:row r="405" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="405" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A405" s="87">
         <x:v>760405</x:v>
       </x:c>
@@ -18802,7 +18802,7 @@
         <x:f>S405*T405</x:f>
       </x:c>
     </x:row>
-    <x:row r="406" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="406" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A406" s="87">
         <x:v>760405</x:v>
       </x:c>
@@ -18842,7 +18842,7 @@
         <x:f>S406*T406</x:f>
       </x:c>
     </x:row>
-    <x:row r="407" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="407" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A407" s="87">
         <x:v>760405</x:v>
       </x:c>
@@ -18882,7 +18882,7 @@
         <x:f>S407*T407</x:f>
       </x:c>
     </x:row>
-    <x:row r="408" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="408" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A408" s="87">
         <x:v>760405</x:v>
       </x:c>
@@ -18922,7 +18922,7 @@
         <x:f>S408*T408</x:f>
       </x:c>
     </x:row>
-    <x:row r="409" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="409" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A409" s="87">
         <x:v>760405</x:v>
       </x:c>
@@ -18962,7 +18962,7 @@
         <x:f>S409*T409</x:f>
       </x:c>
     </x:row>
-    <x:row r="410" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="410" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A410" s="87">
         <x:v>760405</x:v>
       </x:c>
@@ -19002,7 +19002,7 @@
         <x:f>S410*T410</x:f>
       </x:c>
     </x:row>
-    <x:row r="411" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="411" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A411" s="87">
         <x:v>760405</x:v>
       </x:c>
@@ -19042,7 +19042,7 @@
         <x:f>S411*T411</x:f>
       </x:c>
     </x:row>
-    <x:row r="412" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="412" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A412" s="87">
         <x:v>760405</x:v>
       </x:c>
@@ -19082,7 +19082,7 @@
         <x:f>S412*T412</x:f>
       </x:c>
     </x:row>
-    <x:row r="413" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="413" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A413" s="87">
         <x:v>760405</x:v>
       </x:c>
@@ -19122,7 +19122,7 @@
         <x:f>S413*T413</x:f>
       </x:c>
     </x:row>
-    <x:row r="414" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="414" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A414" s="87">
         <x:v>760406</x:v>
       </x:c>
@@ -19162,7 +19162,7 @@
         <x:f>S414*T414</x:f>
       </x:c>
     </x:row>
-    <x:row r="415" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="415" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A415" s="87">
         <x:v>760406</x:v>
       </x:c>
@@ -19202,7 +19202,7 @@
         <x:f>S415*T415</x:f>
       </x:c>
     </x:row>
-    <x:row r="416" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="416" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A416" s="87">
         <x:v>760406</x:v>
       </x:c>
@@ -19242,7 +19242,7 @@
         <x:f>S416*T416</x:f>
       </x:c>
     </x:row>
-    <x:row r="417" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="417" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A417" s="87">
         <x:v>760406</x:v>
       </x:c>
@@ -19282,7 +19282,7 @@
         <x:f>S417*T417</x:f>
       </x:c>
     </x:row>
-    <x:row r="418" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="418" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A418" s="87">
         <x:v>760406</x:v>
       </x:c>
@@ -19322,7 +19322,7 @@
         <x:f>S418*T418</x:f>
       </x:c>
     </x:row>
-    <x:row r="419" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="419" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A419" s="87">
         <x:v>760408</x:v>
       </x:c>
@@ -19362,7 +19362,7 @@
         <x:f>S419*T419</x:f>
       </x:c>
     </x:row>
-    <x:row r="420" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="420" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A420" s="87">
         <x:v>760408</x:v>
       </x:c>
@@ -19402,7 +19402,7 @@
         <x:f>S420*T420</x:f>
       </x:c>
     </x:row>
-    <x:row r="421" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="421" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A421" s="87">
         <x:v>760408</x:v>
       </x:c>
@@ -19442,7 +19442,7 @@
         <x:f>S421*T421</x:f>
       </x:c>
     </x:row>
-    <x:row r="422" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="422" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A422" s="87">
         <x:v>760408</x:v>
       </x:c>
@@ -19482,7 +19482,7 @@
         <x:f>S422*T422</x:f>
       </x:c>
     </x:row>
-    <x:row r="423" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="423" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A423" s="87">
         <x:v>760408</x:v>
       </x:c>
@@ -19522,7 +19522,7 @@
         <x:f>S423*T423</x:f>
       </x:c>
     </x:row>
-    <x:row r="424" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="424" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A424" s="87">
         <x:v>760411</x:v>
       </x:c>
@@ -19562,7 +19562,7 @@
         <x:f>S424*T424</x:f>
       </x:c>
     </x:row>
-    <x:row r="425" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="425" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A425" s="87">
         <x:v>760411</x:v>
       </x:c>
@@ -19602,7 +19602,7 @@
         <x:f>S425*T425</x:f>
       </x:c>
     </x:row>
-    <x:row r="426" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="426" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A426" s="87">
         <x:v>760411</x:v>
       </x:c>
@@ -19642,7 +19642,7 @@
         <x:f>S426*T426</x:f>
       </x:c>
     </x:row>
-    <x:row r="427" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="427" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A427" s="87">
         <x:v>760411</x:v>
       </x:c>
@@ -19682,7 +19682,7 @@
         <x:f>S427*T427</x:f>
       </x:c>
     </x:row>
-    <x:row r="428" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="428" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A428" s="87">
         <x:v>760411</x:v>
       </x:c>
@@ -19722,7 +19722,7 @@
         <x:f>S428*T428</x:f>
       </x:c>
     </x:row>
-    <x:row r="429" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="429" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A429" s="87">
         <x:v>760411</x:v>
       </x:c>
@@ -19762,7 +19762,7 @@
         <x:f>S429*T429</x:f>
       </x:c>
     </x:row>
-    <x:row r="430" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="430" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A430" s="87">
         <x:v>760411</x:v>
       </x:c>
@@ -19802,7 +19802,7 @@
         <x:f>S430*T430</x:f>
       </x:c>
     </x:row>
-    <x:row r="431" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="431" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A431" s="87">
         <x:v>760411</x:v>
       </x:c>
@@ -19842,7 +19842,7 @@
         <x:f>S431*T431</x:f>
       </x:c>
     </x:row>
-    <x:row r="432" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="432" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A432" s="87">
         <x:v>760414</x:v>
       </x:c>
@@ -19882,7 +19882,7 @@
         <x:f>S432*T432</x:f>
       </x:c>
     </x:row>
-    <x:row r="433" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="433" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A433" s="87">
         <x:v>760414</x:v>
       </x:c>
@@ -19922,7 +19922,7 @@
         <x:f>S433*T433</x:f>
       </x:c>
     </x:row>
-    <x:row r="434" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="434" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A434" s="87">
         <x:v>760414</x:v>
       </x:c>
@@ -19962,7 +19962,7 @@
         <x:f>S434*T434</x:f>
       </x:c>
     </x:row>
-    <x:row r="435" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="435" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A435" s="87">
         <x:v>760414</x:v>
       </x:c>
@@ -20002,7 +20002,7 @@
         <x:f>S435*T435</x:f>
       </x:c>
     </x:row>
-    <x:row r="436" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="436" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A436" s="87">
         <x:v>760414</x:v>
       </x:c>
@@ -20042,7 +20042,7 @@
         <x:f>S436*T436</x:f>
       </x:c>
     </x:row>
-    <x:row r="437" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="437" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A437" s="87">
         <x:v>760414</x:v>
       </x:c>
@@ -20082,7 +20082,7 @@
         <x:f>S437*T437</x:f>
       </x:c>
     </x:row>
-    <x:row r="438" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="438" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A438" s="87">
         <x:v>760414</x:v>
       </x:c>
@@ -20122,7 +20122,7 @@
         <x:f>S438*T438</x:f>
       </x:c>
     </x:row>
-    <x:row r="439" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="439" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A439" s="87">
         <x:v>760414</x:v>
       </x:c>
@@ -20162,7 +20162,7 @@
         <x:f>S439*T439</x:f>
       </x:c>
     </x:row>
-    <x:row r="440" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="440" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A440" s="87">
         <x:v>760416</x:v>
       </x:c>
@@ -20202,7 +20202,7 @@
         <x:f>S440*T440</x:f>
       </x:c>
     </x:row>
-    <x:row r="441" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="441" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A441" s="87">
         <x:v>760416</x:v>
       </x:c>
@@ -20242,7 +20242,7 @@
         <x:f>S441*T441</x:f>
       </x:c>
     </x:row>
-    <x:row r="442" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="442" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A442" s="87">
         <x:v>760416</x:v>
       </x:c>
@@ -20282,7 +20282,7 @@
         <x:f>S442*T442</x:f>
       </x:c>
     </x:row>
-    <x:row r="443" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="443" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A443" s="87">
         <x:v>760416</x:v>
       </x:c>
@@ -20322,7 +20322,7 @@
         <x:f>S443*T443</x:f>
       </x:c>
     </x:row>
-    <x:row r="444" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="444" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A444" s="87">
         <x:v>760417</x:v>
       </x:c>
@@ -20362,7 +20362,7 @@
         <x:f>S444*T444</x:f>
       </x:c>
     </x:row>
-    <x:row r="445" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="445" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A445" s="87">
         <x:v>760417</x:v>
       </x:c>
@@ -20402,7 +20402,7 @@
         <x:f>S445*T445</x:f>
       </x:c>
     </x:row>
-    <x:row r="446" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="446" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A446" s="87">
         <x:v>760417</x:v>
       </x:c>
@@ -20442,7 +20442,7 @@
         <x:f>S446*T446</x:f>
       </x:c>
     </x:row>
-    <x:row r="447" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="447" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A447" s="87">
         <x:v>760417</x:v>
       </x:c>
@@ -20482,7 +20482,7 @@
         <x:f>S447*T447</x:f>
       </x:c>
     </x:row>
-    <x:row r="448" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="448" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A448" s="87">
         <x:v>760417</x:v>
       </x:c>
@@ -20522,7 +20522,7 @@
         <x:f>S448*T448</x:f>
       </x:c>
     </x:row>
-    <x:row r="449" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="449" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A449" s="87">
         <x:v>760417</x:v>
       </x:c>
@@ -20562,7 +20562,7 @@
         <x:f>S449*T449</x:f>
       </x:c>
     </x:row>
-    <x:row r="450" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="450" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A450" s="87">
         <x:v>760417</x:v>
       </x:c>
@@ -20602,7 +20602,7 @@
         <x:f>S450*T450</x:f>
       </x:c>
     </x:row>
-    <x:row r="451" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="451" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A451" s="87">
         <x:v>760417</x:v>
       </x:c>
@@ -20642,7 +20642,7 @@
         <x:f>S451*T451</x:f>
       </x:c>
     </x:row>
-    <x:row r="452" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="452" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A452" s="87">
         <x:v>760419</x:v>
       </x:c>
@@ -20682,7 +20682,7 @@
         <x:f>S452*T452</x:f>
       </x:c>
     </x:row>
-    <x:row r="453" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="453" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A453" s="87">
         <x:v>760419</x:v>
       </x:c>
@@ -20722,7 +20722,7 @@
         <x:f>S453*T453</x:f>
       </x:c>
     </x:row>
-    <x:row r="454" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="454" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A454" s="87">
         <x:v>760419</x:v>
       </x:c>
@@ -20762,7 +20762,7 @@
         <x:f>S454*T454</x:f>
       </x:c>
     </x:row>
-    <x:row r="455" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="455" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A455" s="87">
         <x:v>760419</x:v>
       </x:c>
@@ -20802,7 +20802,7 @@
         <x:f>S455*T455</x:f>
       </x:c>
     </x:row>
-    <x:row r="456" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="456" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A456" s="87">
         <x:v>760419</x:v>
       </x:c>
@@ -20842,7 +20842,7 @@
         <x:f>S456*T456</x:f>
       </x:c>
     </x:row>
-    <x:row r="457" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="457" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A457" s="87">
         <x:v>760419</x:v>
       </x:c>
@@ -20882,7 +20882,7 @@
         <x:f>S457*T457</x:f>
       </x:c>
     </x:row>
-    <x:row r="458" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="458" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A458" s="87">
         <x:v>760419</x:v>
       </x:c>
@@ -20922,7 +20922,7 @@
         <x:f>S458*T458</x:f>
       </x:c>
     </x:row>
-    <x:row r="459" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.3">
+    <x:row r="459" spans="1:31" ht="15" customHeight="1" hidden="1" x14ac:dyDescent="0.25">
       <x:c r="A459" s="87">
         <x:v>760419</x:v>
       </x:c>
@@ -20962,7 +20962,7 @@
         <x:f>S459*T459</x:f>
       </x:c>
     </x:row>
-    <x:row r="463" spans="1:31" x14ac:dyDescent="0.3">
+    <x:row r="463" spans="1:31" x14ac:dyDescent="0.2">
       <x:c r="B463" s="55" t="s">
         <x:v>550</x:v>
       </x:c>
@@ -20970,7 +20970,7 @@
         <x:v>551</x:v>
       </x:c>
     </x:row>
-    <x:row r="464" spans="1:31" x14ac:dyDescent="0.3">
+    <x:row r="464" spans="1:31" x14ac:dyDescent="0.2">
       <x:c r="B464" s="55" t="s">
         <x:v>552</x:v>
       </x:c>
@@ -20978,7 +20978,7 @@
         <x:v>553</x:v>
       </x:c>
     </x:row>
-    <x:row r="465" spans="1:31" x14ac:dyDescent="0.3">
+    <x:row r="465" spans="1:31" x14ac:dyDescent="0.2">
       <x:c r="B465" s="55" t="s">
         <x:v>554</x:v>
       </x:c>
@@ -20986,7 +20986,7 @@
         <x:v>555</x:v>
       </x:c>
     </x:row>
-    <x:row r="466" spans="1:31" x14ac:dyDescent="0.3">
+    <x:row r="466" spans="1:31" x14ac:dyDescent="0.2">
       <x:c r="B466" s="55" t="s">
         <x:v>556</x:v>
       </x:c>
@@ -21018,7 +21018,7 @@
   </x:mergeCells>
   <x:phoneticPr fontId="20" type="noConversion"/>
   <x:hyperlinks>
-    <x:hyperlink ref="E5" r:id="rId11"/>
+    <x:hyperlink ref="E5" r:id="rId9"/>
   </x:hyperlinks>
   <x:printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.5905511811023623" bottom="0.5905511811023623" header="0.31496062992125984" footer="0.15748031496062992"/>
@@ -21048,6 +21048,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010099C01A7CBCC89E43BECB694AF5E0D618" ma:contentTypeVersion="19" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="a4b4f7574745c41f0256e598d6209459">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e428a92d-3fc5-4a74-9eb5-a846bf6af7b4" xmlns:ns3="1877f7ac-3b54-4345-a0fb-3ef760a60102" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4041210650f2e49e98ea315b29a8d5be" ns2:_="" ns3:_="">
     <xsd:import namespace="e428a92d-3fc5-4a74-9eb5-a846bf6af7b4"/>
@@ -21308,15 +21317,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAC9DBDF-E304-4B61-A23F-5BFA34A4AAE3}">
   <ds:schemaRefs>
@@ -21335,6 +21335,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{607ADB5E-106C-4F31-86AB-4704764E8CC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D7D8236-9CB6-46B8-B25E-8313D5F700EF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21351,12 +21359,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{607ADB5E-106C-4F31-86AB-4704764E8CC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/src/BexioOrderImport.Tests/AnonymizedOrder.xlsx
+++ b/src/BexioOrderImport.Tests/AnonymizedOrder.xlsx
@@ -21018,7 +21018,7 @@
   </x:mergeCells>
   <x:phoneticPr fontId="20" type="noConversion"/>
   <x:hyperlinks>
-    <x:hyperlink ref="E5" r:id="rId9"/>
+    <x:hyperlink ref="E5" r:id="rId11"/>
   </x:hyperlinks>
   <x:printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.5905511811023623" bottom="0.5905511811023623" header="0.31496062992125984" footer="0.15748031496062992"/>

--- a/src/BexioOrderImport.Tests/AnonymizedOrder.xlsx
+++ b/src/BexioOrderImport.Tests/AnonymizedOrder.xlsx
@@ -21018,7 +21018,7 @@
   </x:mergeCells>
   <x:phoneticPr fontId="20" type="noConversion"/>
   <x:hyperlinks>
-    <x:hyperlink ref="E5" r:id="rId11"/>
+    <x:hyperlink ref="E5" r:id="rId10"/>
   </x:hyperlinks>
   <x:printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.5905511811023623" bottom="0.5905511811023623" header="0.31496062992125984" footer="0.15748031496062992"/>
